--- a/年度计划表.xlsx
+++ b/年度计划表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kayla/Desktop/Workspace/kayla00822.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF268F0-5B80-E94E-87EC-B3B49A7B4226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D6DD98-CFB5-0F49-8DC6-A7171D0E2168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2022书单表" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="254">
   <si>
     <t>序号</t>
   </si>
@@ -855,6 +855,46 @@
   </si>
   <si>
     <t>投递简历&amp;寻找大机构的机会</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>《尼罗河上的惨案》</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>《阿甘正传》</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>《教父1》</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>影院</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>在影片中，尼罗河上迷人的风光背后，是人们对于金钱和权利的追逐。一点感触是：人们对于财富的争夺总是飞蛾扑火般，而在财富中心的人始终无法平静。有趣的是，影片昏黄色的色调总是让我想起六年级在图书馆借阅的探索书刊，里面的人物都是金色卷发，他们在金字塔、巴比伦进行着探索与冒险，让小小的我觉得神奇不已。</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿甘是一个不那么优秀的孩子，但是他有幸在时代的洪流中保留了自己的虔诚和朴实，尽管在爱情中无法得到珍妮的慰藉，但是正因如此，他始终保持了对于生活的向往和动力，他是幸福的。</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>实体书</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>文学类</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>《平凡的世界》一</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>在西西弗斯书店读完了平凡的世界第一本，书中描写的上个世纪在一个贫困的山村中，一家人如何生存。读着读着，仿佛是在看自己家族的兴衰史，家中的大姨总是无论如何也要在时代中拼搏前进，我妈也在这个时代中不断的顽强向前。仿佛是在读自己家中的故事。</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
@@ -1208,7 +1248,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="171">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1407,9 +1447,6 @@
     <xf numFmtId="176" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1530,6 +1567,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1685,6 +1725,42 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1969,18 +2045,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:J5"/>
+  <dimension ref="B1:J6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10" style="91"/>
-    <col min="2" max="2" width="9.6640625" style="91" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" style="91" customWidth="1"/>
-    <col min="4" max="4" width="13.83203125" style="91" customWidth="1"/>
-    <col min="5" max="5" width="21.6640625" style="91" customWidth="1"/>
-    <col min="6" max="6" width="20.6640625" style="91" customWidth="1"/>
-    <col min="7" max="7" width="21" style="103" customWidth="1"/>
-    <col min="8" max="8" width="70.1640625" style="99" customWidth="1"/>
-    <col min="9" max="16384" width="10" style="91"/>
+    <col min="1" max="1" width="10" style="90"/>
+    <col min="2" max="2" width="9.6640625" style="90" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" style="90" customWidth="1"/>
+    <col min="4" max="4" width="13.83203125" style="90" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" style="90" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" style="90" customWidth="1"/>
+    <col min="7" max="7" width="21" style="102" customWidth="1"/>
+    <col min="8" max="8" width="70.1640625" style="98" customWidth="1"/>
+    <col min="9" max="16384" width="10" style="90"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="78" customHeight="1">
@@ -1995,99 +2071,122 @@
       <c r="H1" s="108"/>
     </row>
     <row r="2" spans="2:10" ht="20" customHeight="1">
-      <c r="B2" s="92" t="s">
+      <c r="B2" s="91" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="92" t="s">
+      <c r="C2" s="91" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="92" t="s">
+      <c r="D2" s="91" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="92" t="s">
+      <c r="E2" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="92" t="s">
+      <c r="F2" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="100" t="s">
+      <c r="G2" s="99" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="92" t="s">
+      <c r="H2" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
     </row>
     <row r="3" spans="2:10" ht="89" customHeight="1">
-      <c r="B3" s="94">
+      <c r="B3" s="93">
         <v>1</v>
       </c>
-      <c r="C3" s="94" t="s">
+      <c r="C3" s="93" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="94" t="s">
+      <c r="D3" s="93" t="s">
         <v>231</v>
       </c>
-      <c r="E3" s="94" t="s">
+      <c r="E3" s="93" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="94" t="s">
+      <c r="F3" s="93" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="102">
+      <c r="G3" s="101">
         <v>44570</v>
       </c>
-      <c r="H3" s="96" t="s">
+      <c r="H3" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="101"/>
-      <c r="J3" s="101"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="100"/>
     </row>
     <row r="4" spans="2:10" ht="128" customHeight="1">
-      <c r="B4" s="94">
+      <c r="B4" s="93">
         <v>2</v>
       </c>
-      <c r="C4" s="94" t="s">
+      <c r="C4" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="94" t="s">
+      <c r="D4" s="93" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="94" t="s">
+      <c r="E4" s="93" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="94" t="s">
+      <c r="F4" s="93" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="102">
+      <c r="G4" s="101">
         <v>44577</v>
       </c>
-      <c r="H4" s="96" t="s">
+      <c r="H4" s="95" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="2:10" ht="200" customHeight="1">
-      <c r="B5" s="94">
+      <c r="B5" s="93">
         <v>3</v>
       </c>
-      <c r="C5" s="94" t="s">
+      <c r="C5" s="93" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="94" t="s">
+      <c r="D5" s="93" t="s">
         <v>231</v>
       </c>
-      <c r="E5" s="94" t="s">
+      <c r="E5" s="93" t="s">
         <v>230</v>
       </c>
-      <c r="F5" s="94" t="s">
+      <c r="F5" s="93" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="102">
+      <c r="G5" s="101">
         <v>44591</v>
       </c>
-      <c r="H5" s="96" t="s">
+      <c r="H5" s="95" t="s">
         <v>232</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" ht="90" customHeight="1">
+      <c r="B6" s="93">
+        <v>4</v>
+      </c>
+      <c r="C6" s="93" t="s">
+        <v>251</v>
+      </c>
+      <c r="D6" s="93" t="s">
+        <v>231</v>
+      </c>
+      <c r="E6" s="93" t="s">
+        <v>252</v>
+      </c>
+      <c r="F6" s="93" t="s">
+        <v>250</v>
+      </c>
+      <c r="G6" s="101">
+        <v>44619</v>
+      </c>
+      <c r="H6" s="95" t="s">
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -2101,21 +2200,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:XFB8"/>
+  <dimension ref="A1:XFB11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" style="91" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" style="91" customWidth="1"/>
-    <col min="3" max="3" width="24.1640625" style="91" customWidth="1"/>
-    <col min="4" max="4" width="16.33203125" style="91" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" style="91" customWidth="1"/>
-    <col min="6" max="6" width="21" style="98" customWidth="1"/>
-    <col min="7" max="7" width="64" style="99" customWidth="1"/>
-    <col min="8" max="16382" width="10" style="91"/>
-    <col min="16383" max="16384" width="10" style="97"/>
+    <col min="1" max="1" width="9.6640625" style="90" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" style="90" customWidth="1"/>
+    <col min="3" max="3" width="24.1640625" style="90" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" style="90" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" style="90" customWidth="1"/>
+    <col min="6" max="6" width="21" style="97" customWidth="1"/>
+    <col min="7" max="7" width="64" style="98" customWidth="1"/>
+    <col min="8" max="16382" width="10" style="90"/>
+    <col min="16383" max="16384" width="10" style="96"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="91" customFormat="1" ht="78" customHeight="1">
+    <row r="1" spans="1:7" s="90" customFormat="1" ht="78" customHeight="1">
       <c r="A1" s="109" t="s">
         <v>223</v>
       </c>
@@ -2126,166 +2225,233 @@
       <c r="F1" s="111"/>
       <c r="G1" s="112"/>
     </row>
-    <row r="2" spans="1:7" s="91" customFormat="1" ht="20" customHeight="1">
-      <c r="A2" s="92" t="s">
+    <row r="2" spans="1:7" s="90" customFormat="1" ht="20" customHeight="1">
+      <c r="A2" s="91" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="92" t="s">
+      <c r="B2" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="92" t="s">
+      <c r="C2" s="91" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="92" t="s">
+      <c r="D2" s="91" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="92" t="s">
+      <c r="E2" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="93" t="s">
+      <c r="F2" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="92" t="s">
+      <c r="G2" s="91" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="91" customFormat="1" ht="141" customHeight="1">
-      <c r="A3" s="94">
+    <row r="3" spans="1:7" s="90" customFormat="1" ht="141" customHeight="1">
+      <c r="A3" s="93">
         <v>1</v>
       </c>
-      <c r="B3" s="94" t="s">
+      <c r="B3" s="93" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="94" t="s">
+      <c r="C3" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="94" t="s">
+      <c r="D3" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="94" t="s">
+      <c r="E3" s="93" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="95">
+      <c r="F3" s="94">
         <v>44575</v>
       </c>
-      <c r="G3" s="96" t="s">
+      <c r="G3" s="95" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="96" customHeight="1">
-      <c r="A4" s="94">
+      <c r="A4" s="93">
         <v>2</v>
       </c>
-      <c r="B4" s="94" t="s">
+      <c r="B4" s="93" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="94" t="s">
+      <c r="C4" s="93" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="94" t="s">
+      <c r="D4" s="93" t="s">
         <v>226</v>
       </c>
-      <c r="E4" s="94" t="s">
+      <c r="E4" s="93" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="95">
+      <c r="F4" s="94">
         <v>44582</v>
       </c>
-      <c r="G4" s="96" t="s">
+      <c r="G4" s="95" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="20" customHeight="1">
-      <c r="A5" s="94">
+      <c r="A5" s="93">
         <v>3</v>
       </c>
-      <c r="B5" s="94" t="s">
+      <c r="B5" s="93" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="94" t="s">
+      <c r="C5" s="93" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="94" t="s">
+      <c r="D5" s="93" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="94" t="s">
+      <c r="E5" s="93" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="95">
+      <c r="F5" s="94">
         <v>44583</v>
       </c>
-      <c r="G5" s="96" t="s">
+      <c r="G5" s="95" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="143" customHeight="1">
-      <c r="A6" s="94">
+      <c r="A6" s="93">
         <v>4</v>
       </c>
-      <c r="B6" s="94" t="s">
+      <c r="B6" s="93" t="s">
         <v>225</v>
       </c>
-      <c r="C6" s="94" t="s">
+      <c r="C6" s="93" t="s">
         <v>224</v>
       </c>
-      <c r="D6" s="94" t="s">
+      <c r="D6" s="93" t="s">
         <v>226</v>
       </c>
-      <c r="E6" s="94" t="s">
+      <c r="E6" s="93" t="s">
         <v>227</v>
       </c>
-      <c r="F6" s="95">
+      <c r="F6" s="94">
         <v>44596</v>
       </c>
-      <c r="G6" s="96" t="s">
+      <c r="G6" s="95" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="160" customHeight="1">
-      <c r="A7" s="94">
+      <c r="A7" s="93">
         <v>5</v>
       </c>
-      <c r="B7" s="94" t="s">
+      <c r="B7" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="C7" s="94" t="s">
+      <c r="C7" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="D7" s="94" t="s">
+      <c r="D7" s="93" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="94" t="s">
+      <c r="E7" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="F7" s="95">
+      <c r="F7" s="94">
         <v>44603</v>
       </c>
-      <c r="G7" s="96" t="s">
+      <c r="G7" s="95" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="54" customHeight="1">
-      <c r="A8" s="94">
+      <c r="A8" s="93">
         <v>6</v>
       </c>
-      <c r="B8" s="94" t="s">
+      <c r="B8" s="93" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="94" t="s">
+      <c r="C8" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="D8" s="94" t="s">
+      <c r="D8" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="94" t="s">
+      <c r="E8" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="F8" s="95">
+      <c r="F8" s="94">
         <v>44603</v>
       </c>
-      <c r="G8" s="96" t="s">
+      <c r="G8" s="95" t="s">
         <v>240</v>
       </c>
+    </row>
+    <row r="9" spans="1:7" ht="104" customHeight="1">
+      <c r="A9" s="93">
+        <v>7</v>
+      </c>
+      <c r="B9" s="93" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="93" t="s">
+        <v>244</v>
+      </c>
+      <c r="D9" s="93" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="93" t="s">
+        <v>247</v>
+      </c>
+      <c r="F9" s="94">
+        <v>44610</v>
+      </c>
+      <c r="G9" s="95" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="78" customHeight="1">
+      <c r="A10" s="93">
+        <v>8</v>
+      </c>
+      <c r="B10" s="93" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="D10" s="93" t="s">
+        <v>226</v>
+      </c>
+      <c r="E10" s="93" t="s">
+        <v>236</v>
+      </c>
+      <c r="F10" s="94">
+        <v>44611</v>
+      </c>
+      <c r="G10" s="95" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="20" customHeight="1">
+      <c r="A11" s="93">
+        <v>9</v>
+      </c>
+      <c r="B11" s="93" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="93" t="s">
+        <v>246</v>
+      </c>
+      <c r="D11" s="93" t="s">
+        <v>226</v>
+      </c>
+      <c r="E11" s="93" t="s">
+        <v>236</v>
+      </c>
+      <c r="F11" s="94">
+        <v>44619</v>
+      </c>
+      <c r="G11" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2382,137 +2548,137 @@
       </c>
       <c r="J5" s="48"/>
     </row>
-    <row r="6" spans="2:10" s="27" customFormat="1" ht="50" customHeight="1">
-      <c r="B6" s="57">
+    <row r="6" spans="2:10" ht="50" customHeight="1">
+      <c r="B6" s="166">
         <v>1</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="167" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="58" t="s">
+      <c r="D6" s="167" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="64">
+      <c r="E6" s="168">
         <v>44544</v>
       </c>
-      <c r="F6" s="65">
+      <c r="F6" s="169">
         <v>20</v>
       </c>
-      <c r="G6" s="66" t="s">
+      <c r="G6" s="170" t="s">
         <v>50</v>
       </c>
-      <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-    </row>
-    <row r="7" spans="2:10" s="27" customFormat="1" ht="50" customHeight="1">
-      <c r="B7" s="57">
+      <c r="H6" s="106"/>
+      <c r="I6" s="106"/>
+    </row>
+    <row r="7" spans="2:10" ht="50" customHeight="1">
+      <c r="B7" s="166">
         <v>2</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="167" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="58" t="s">
+      <c r="D7" s="167" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="64">
+      <c r="E7" s="168">
         <v>44550</v>
       </c>
-      <c r="F7" s="65">
+      <c r="F7" s="169">
         <v>15</v>
       </c>
-      <c r="G7" s="66" t="s">
+      <c r="G7" s="170" t="s">
         <v>51</v>
       </c>
-      <c r="H7" s="67"/>
-      <c r="I7" s="67"/>
-    </row>
-    <row r="8" spans="2:10" s="27" customFormat="1" ht="50" customHeight="1">
-      <c r="B8" s="57">
+      <c r="H7" s="106"/>
+      <c r="I7" s="106"/>
+    </row>
+    <row r="8" spans="2:10" ht="50" customHeight="1">
+      <c r="B8" s="166">
         <v>3</v>
       </c>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="167" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="58" t="s">
+      <c r="D8" s="167" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="64">
+      <c r="E8" s="168">
         <v>44560</v>
       </c>
-      <c r="F8" s="65">
+      <c r="F8" s="169">
         <v>25</v>
       </c>
-      <c r="G8" s="68" t="s">
+      <c r="G8" s="77" t="s">
         <v>52</v>
       </c>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
-    </row>
-    <row r="9" spans="2:10" s="27" customFormat="1" ht="50" customHeight="1">
-      <c r="B9" s="57">
+      <c r="H8" s="106"/>
+      <c r="I8" s="106"/>
+    </row>
+    <row r="9" spans="2:10" ht="50" customHeight="1">
+      <c r="B9" s="166">
         <v>4</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="167" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="58" t="s">
+      <c r="D9" s="167" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="64">
+      <c r="E9" s="168">
         <v>44561</v>
       </c>
-      <c r="F9" s="65">
+      <c r="F9" s="169">
         <v>30</v>
       </c>
-      <c r="G9" s="68" t="s">
+      <c r="G9" s="77" t="s">
         <v>53</v>
       </c>
-      <c r="H9" s="67"/>
-      <c r="I9" s="67"/>
-    </row>
-    <row r="10" spans="2:10" s="27" customFormat="1" ht="50" customHeight="1">
-      <c r="B10" s="57">
+      <c r="H9" s="106"/>
+      <c r="I9" s="106"/>
+    </row>
+    <row r="10" spans="2:10" ht="50" customHeight="1">
+      <c r="B10" s="166">
         <v>5</v>
       </c>
-      <c r="C10" s="58" t="s">
+      <c r="C10" s="167" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="58" t="s">
+      <c r="D10" s="167" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="64">
+      <c r="E10" s="168">
         <v>44564</v>
       </c>
-      <c r="F10" s="65" t="s">
+      <c r="F10" s="169" t="s">
         <v>54</v>
       </c>
-      <c r="G10" s="68" t="s">
+      <c r="G10" s="77" t="s">
         <v>55</v>
       </c>
-      <c r="H10" s="67"/>
-      <c r="I10" s="67"/>
-    </row>
-    <row r="11" spans="2:10" s="27" customFormat="1" ht="50" customHeight="1">
-      <c r="B11" s="57">
+      <c r="H10" s="106"/>
+      <c r="I10" s="106"/>
+    </row>
+    <row r="11" spans="2:10" ht="50" customHeight="1">
+      <c r="B11" s="166">
         <v>5</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="167" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="58" t="s">
+      <c r="D11" s="167" t="s">
         <v>49</v>
       </c>
-      <c r="E11" s="64">
+      <c r="E11" s="168">
         <v>44569</v>
       </c>
-      <c r="F11" s="65" t="s">
+      <c r="F11" s="169" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="68" t="s">
+      <c r="G11" s="77" t="s">
         <v>56</v>
       </c>
-      <c r="H11" s="67"/>
-      <c r="I11" s="67"/>
+      <c r="H11" s="106"/>
+      <c r="I11" s="106"/>
     </row>
     <row r="12" spans="2:10" s="27" customFormat="1" ht="50" customHeight="1">
       <c r="B12" s="57"/>
@@ -2520,9 +2686,9 @@
       <c r="D12" s="58"/>
       <c r="E12" s="64"/>
       <c r="F12" s="65"/>
-      <c r="G12" s="68"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="66"/>
+      <c r="I12" s="66"/>
     </row>
     <row r="13" spans="2:10" s="27" customFormat="1" ht="50" customHeight="1">
       <c r="B13" s="57"/>
@@ -2530,9 +2696,9 @@
       <c r="D13" s="58"/>
       <c r="E13" s="64"/>
       <c r="F13" s="65"/>
-      <c r="G13" s="68"/>
-      <c r="H13" s="67"/>
-      <c r="I13" s="67"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="66"/>
+      <c r="I13" s="66"/>
     </row>
     <row r="14" spans="2:10" s="27" customFormat="1" ht="50" customHeight="1">
       <c r="B14" s="57"/>
@@ -2540,9 +2706,9 @@
       <c r="D14" s="58"/>
       <c r="E14" s="64"/>
       <c r="F14" s="65"/>
-      <c r="G14" s="68"/>
-      <c r="H14" s="67"/>
-      <c r="I14" s="67"/>
+      <c r="G14" s="67"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="66"/>
     </row>
     <row r="15" spans="2:10" s="27" customFormat="1" ht="50" customHeight="1">
       <c r="B15" s="57"/>
@@ -2550,9 +2716,9 @@
       <c r="D15" s="58"/>
       <c r="E15" s="64"/>
       <c r="F15" s="65"/>
-      <c r="G15" s="68"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="67"/>
+      <c r="G15" s="67"/>
+      <c r="H15" s="66"/>
+      <c r="I15" s="66"/>
     </row>
     <row r="16" spans="2:10" s="27" customFormat="1" ht="50" customHeight="1">
       <c r="B16" s="57"/>
@@ -2560,9 +2726,9 @@
       <c r="D16" s="58"/>
       <c r="E16" s="64"/>
       <c r="F16" s="65"/>
-      <c r="G16" s="68"/>
-      <c r="H16" s="67"/>
-      <c r="I16" s="67"/>
+      <c r="G16" s="67"/>
+      <c r="H16" s="66"/>
+      <c r="I16" s="66"/>
     </row>
     <row r="17" spans="2:9" s="27" customFormat="1" ht="50" customHeight="1">
       <c r="B17" s="57"/>
@@ -2570,9 +2736,9 @@
       <c r="D17" s="58"/>
       <c r="E17" s="64"/>
       <c r="F17" s="65"/>
-      <c r="G17" s="68"/>
-      <c r="H17" s="67"/>
-      <c r="I17" s="67"/>
+      <c r="G17" s="67"/>
+      <c r="H17" s="66"/>
+      <c r="I17" s="66"/>
     </row>
     <row r="18" spans="2:9" s="27" customFormat="1" ht="50" customHeight="1">
       <c r="B18" s="57"/>
@@ -2580,9 +2746,9 @@
       <c r="D18" s="58"/>
       <c r="E18" s="64"/>
       <c r="F18" s="65"/>
-      <c r="G18" s="68"/>
-      <c r="H18" s="67"/>
-      <c r="I18" s="67"/>
+      <c r="G18" s="67"/>
+      <c r="H18" s="66"/>
+      <c r="I18" s="66"/>
     </row>
     <row r="19" spans="2:9" s="27" customFormat="1" ht="50" customHeight="1">
       <c r="B19" s="57"/>
@@ -2590,9 +2756,9 @@
       <c r="D19" s="58"/>
       <c r="E19" s="64"/>
       <c r="F19" s="65"/>
-      <c r="G19" s="68"/>
-      <c r="H19" s="67"/>
-      <c r="I19" s="67"/>
+      <c r="G19" s="67"/>
+      <c r="H19" s="66"/>
+      <c r="I19" s="66"/>
     </row>
     <row r="20" spans="2:9" s="27" customFormat="1" ht="50" customHeight="1">
       <c r="B20" s="57"/>
@@ -2600,9 +2766,9 @@
       <c r="D20" s="58"/>
       <c r="E20" s="64"/>
       <c r="F20" s="65"/>
-      <c r="G20" s="68"/>
-      <c r="H20" s="67"/>
-      <c r="I20" s="67"/>
+      <c r="G20" s="67"/>
+      <c r="H20" s="66"/>
+      <c r="I20" s="66"/>
     </row>
     <row r="21" spans="2:9" s="27" customFormat="1" ht="50" customHeight="1">
       <c r="B21" s="57"/>
@@ -2610,9 +2776,9 @@
       <c r="D21" s="58"/>
       <c r="E21" s="64"/>
       <c r="F21" s="65"/>
-      <c r="G21" s="68"/>
-      <c r="H21" s="67"/>
-      <c r="I21" s="67"/>
+      <c r="G21" s="67"/>
+      <c r="H21" s="66"/>
+      <c r="I21" s="66"/>
     </row>
     <row r="22" spans="2:9" s="27" customFormat="1" ht="50" customHeight="1">
       <c r="B22" s="57"/>
@@ -2620,9 +2786,9 @@
       <c r="D22" s="58"/>
       <c r="E22" s="64"/>
       <c r="F22" s="65"/>
-      <c r="G22" s="68"/>
-      <c r="H22" s="67"/>
-      <c r="I22" s="67"/>
+      <c r="G22" s="67"/>
+      <c r="H22" s="66"/>
+      <c r="I22" s="66"/>
     </row>
     <row r="23" spans="2:9" s="27" customFormat="1" ht="50" customHeight="1">
       <c r="B23" s="57"/>
@@ -2630,9 +2796,9 @@
       <c r="D23" s="58"/>
       <c r="E23" s="64"/>
       <c r="F23" s="65"/>
-      <c r="G23" s="68"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="67"/>
+      <c r="G23" s="67"/>
+      <c r="H23" s="66"/>
+      <c r="I23" s="66"/>
     </row>
     <row r="24" spans="2:9" s="27" customFormat="1" ht="50" customHeight="1">
       <c r="B24" s="57"/>
@@ -2640,9 +2806,9 @@
       <c r="D24" s="58"/>
       <c r="E24" s="64"/>
       <c r="F24" s="65"/>
-      <c r="G24" s="68"/>
-      <c r="H24" s="67"/>
-      <c r="I24" s="67"/>
+      <c r="G24" s="67"/>
+      <c r="H24" s="66"/>
+      <c r="I24" s="66"/>
     </row>
     <row r="25" spans="2:9" s="27" customFormat="1" ht="50" customHeight="1">
       <c r="B25" s="57"/>
@@ -2650,9 +2816,9 @@
       <c r="D25" s="58"/>
       <c r="E25" s="64"/>
       <c r="F25" s="65"/>
-      <c r="G25" s="68"/>
-      <c r="H25" s="67"/>
-      <c r="I25" s="67"/>
+      <c r="G25" s="67"/>
+      <c r="H25" s="66"/>
+      <c r="I25" s="66"/>
     </row>
     <row r="26" spans="2:9" s="27" customFormat="1" ht="50" customHeight="1">
       <c r="B26" s="57"/>
@@ -2660,9 +2826,9 @@
       <c r="D26" s="58"/>
       <c r="E26" s="64"/>
       <c r="F26" s="65"/>
-      <c r="G26" s="68"/>
-      <c r="H26" s="67"/>
-      <c r="I26" s="67"/>
+      <c r="G26" s="67"/>
+      <c r="H26" s="66"/>
+      <c r="I26" s="66"/>
     </row>
     <row r="27" spans="2:9" s="27" customFormat="1" ht="50" customHeight="1">
       <c r="B27" s="33"/>
@@ -2670,17 +2836,17 @@
       <c r="D27" s="34"/>
       <c r="E27" s="61"/>
       <c r="F27" s="62"/>
-      <c r="G27" s="69"/>
-      <c r="H27" s="67"/>
-      <c r="I27" s="67"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="66"/>
+      <c r="I27" s="66"/>
     </row>
     <row r="28" spans="2:9" s="51" customFormat="1" ht="30" customHeight="1">
       <c r="B28" s="59"/>
       <c r="C28" s="129"/>
       <c r="D28" s="129"/>
-      <c r="E28" s="70"/>
-      <c r="F28" s="71"/>
-      <c r="G28" s="72"/>
+      <c r="E28" s="69"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="71"/>
       <c r="H28" s="45"/>
       <c r="I28" s="45"/>
     </row>
@@ -2688,9 +2854,9 @@
       <c r="B29" s="59"/>
       <c r="C29" s="130"/>
       <c r="D29" s="130"/>
-      <c r="E29" s="70"/>
-      <c r="F29" s="71"/>
-      <c r="G29" s="72"/>
+      <c r="E29" s="69"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="71"/>
       <c r="H29" s="45"/>
       <c r="I29" s="45"/>
     </row>
@@ -2698,9 +2864,9 @@
       <c r="B30" s="59"/>
       <c r="C30" s="130"/>
       <c r="D30" s="130"/>
-      <c r="E30" s="70"/>
-      <c r="F30" s="71"/>
-      <c r="G30" s="72"/>
+      <c r="E30" s="69"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="71"/>
       <c r="H30" s="45"/>
       <c r="I30" s="45"/>
     </row>
@@ -2708,19 +2874,19 @@
       <c r="B31" s="59"/>
       <c r="C31" s="130"/>
       <c r="D31" s="130"/>
-      <c r="E31" s="70"/>
-      <c r="F31" s="71"/>
-      <c r="G31" s="72"/>
-      <c r="H31" s="67"/>
-      <c r="I31" s="67"/>
+      <c r="E31" s="69"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="66"/>
+      <c r="I31" s="66"/>
     </row>
     <row r="32" spans="2:9" s="48" customFormat="1" ht="30" customHeight="1">
       <c r="B32" s="59"/>
       <c r="C32" s="130"/>
       <c r="D32" s="130"/>
-      <c r="E32" s="73"/>
-      <c r="F32" s="74"/>
-      <c r="G32" s="68"/>
+      <c r="E32" s="72"/>
+      <c r="F32" s="73"/>
+      <c r="G32" s="67"/>
       <c r="H32" s="127"/>
       <c r="I32" s="127"/>
     </row>
@@ -2728,9 +2894,9 @@
       <c r="B33" s="59"/>
       <c r="C33" s="130"/>
       <c r="D33" s="130"/>
-      <c r="E33" s="70"/>
-      <c r="F33" s="74"/>
-      <c r="G33" s="68"/>
+      <c r="E33" s="69"/>
+      <c r="F33" s="73"/>
+      <c r="G33" s="67"/>
       <c r="H33" s="127"/>
       <c r="I33" s="127"/>
     </row>
@@ -2738,9 +2904,9 @@
       <c r="B34" s="59"/>
       <c r="C34" s="130"/>
       <c r="D34" s="130"/>
-      <c r="E34" s="70"/>
-      <c r="F34" s="76"/>
-      <c r="G34" s="68"/>
+      <c r="E34" s="69"/>
+      <c r="F34" s="75"/>
+      <c r="G34" s="67"/>
       <c r="H34" s="128"/>
       <c r="I34" s="128"/>
     </row>
@@ -2748,29 +2914,29 @@
       <c r="B35" s="59"/>
       <c r="C35" s="130"/>
       <c r="D35" s="130"/>
-      <c r="E35" s="70"/>
-      <c r="F35" s="76"/>
-      <c r="G35" s="78"/>
-      <c r="H35" s="75"/>
-      <c r="I35" s="75"/>
+      <c r="E35" s="69"/>
+      <c r="F35" s="75"/>
+      <c r="G35" s="77"/>
+      <c r="H35" s="74"/>
+      <c r="I35" s="74"/>
     </row>
     <row r="36" spans="2:10" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B36" s="59"/>
       <c r="C36" s="130"/>
       <c r="D36" s="130"/>
-      <c r="E36" s="70"/>
-      <c r="F36" s="76"/>
-      <c r="G36" s="78"/>
-      <c r="H36" s="75"/>
-      <c r="I36" s="75"/>
+      <c r="E36" s="69"/>
+      <c r="F36" s="75"/>
+      <c r="G36" s="77"/>
+      <c r="H36" s="74"/>
+      <c r="I36" s="74"/>
     </row>
     <row r="37" spans="2:10" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B37" s="59"/>
       <c r="C37" s="131"/>
       <c r="D37" s="131"/>
-      <c r="E37" s="70"/>
-      <c r="F37" s="76"/>
-      <c r="G37" s="78"/>
+      <c r="E37" s="69"/>
+      <c r="F37" s="75"/>
+      <c r="G37" s="77"/>
       <c r="H37" s="127"/>
       <c r="I37" s="127"/>
     </row>
@@ -2778,19 +2944,19 @@
       <c r="B38" s="60"/>
       <c r="C38" s="132"/>
       <c r="D38" s="138"/>
-      <c r="E38" s="79"/>
-      <c r="F38" s="76"/>
-      <c r="G38" s="68"/>
-      <c r="H38" s="75"/>
-      <c r="I38" s="75"/>
+      <c r="E38" s="78"/>
+      <c r="F38" s="75"/>
+      <c r="G38" s="67"/>
+      <c r="H38" s="74"/>
+      <c r="I38" s="74"/>
     </row>
     <row r="39" spans="2:10" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B39" s="60"/>
       <c r="C39" s="133"/>
       <c r="D39" s="139"/>
-      <c r="E39" s="79"/>
-      <c r="F39" s="76"/>
-      <c r="G39" s="68"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="75"/>
+      <c r="G39" s="67"/>
       <c r="H39" s="128"/>
       <c r="I39" s="128"/>
     </row>
@@ -2798,490 +2964,490 @@
       <c r="B40" s="60"/>
       <c r="C40" s="133"/>
       <c r="D40" s="139"/>
-      <c r="E40" s="79"/>
-      <c r="F40" s="76"/>
-      <c r="G40" s="68"/>
-      <c r="H40" s="75"/>
-      <c r="I40" s="77"/>
-      <c r="J40" s="85"/>
+      <c r="E40" s="78"/>
+      <c r="F40" s="75"/>
+      <c r="G40" s="67"/>
+      <c r="H40" s="74"/>
+      <c r="I40" s="76"/>
+      <c r="J40" s="84"/>
     </row>
     <row r="41" spans="2:10" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B41" s="60"/>
       <c r="C41" s="133"/>
       <c r="D41" s="139"/>
-      <c r="E41" s="79"/>
-      <c r="F41" s="76"/>
-      <c r="G41" s="68"/>
+      <c r="E41" s="78"/>
+      <c r="F41" s="75"/>
+      <c r="G41" s="67"/>
       <c r="H41" s="128"/>
       <c r="I41" s="128"/>
-      <c r="J41" s="85"/>
+      <c r="J41" s="84"/>
     </row>
     <row r="42" spans="2:10" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B42" s="60"/>
       <c r="C42" s="133"/>
       <c r="D42" s="139"/>
-      <c r="E42" s="79"/>
-      <c r="F42" s="76"/>
-      <c r="G42" s="68"/>
+      <c r="E42" s="78"/>
+      <c r="F42" s="75"/>
+      <c r="G42" s="67"/>
       <c r="H42" s="128"/>
       <c r="I42" s="128"/>
-      <c r="J42" s="85"/>
+      <c r="J42" s="84"/>
     </row>
     <row r="43" spans="2:10" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B43" s="60"/>
       <c r="C43" s="133"/>
       <c r="D43" s="139"/>
-      <c r="E43" s="79"/>
-      <c r="F43" s="76"/>
-      <c r="G43" s="68"/>
+      <c r="E43" s="78"/>
+      <c r="F43" s="75"/>
+      <c r="G43" s="67"/>
       <c r="H43" s="128"/>
       <c r="I43" s="128"/>
-      <c r="J43" s="85"/>
+      <c r="J43" s="84"/>
     </row>
     <row r="44" spans="2:10" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B44" s="60"/>
       <c r="C44" s="133"/>
       <c r="D44" s="139"/>
-      <c r="E44" s="79"/>
-      <c r="F44" s="76"/>
-      <c r="G44" s="68"/>
-      <c r="H44" s="77"/>
-      <c r="I44" s="77"/>
-      <c r="J44" s="85"/>
+      <c r="E44" s="78"/>
+      <c r="F44" s="75"/>
+      <c r="G44" s="67"/>
+      <c r="H44" s="76"/>
+      <c r="I44" s="76"/>
+      <c r="J44" s="84"/>
     </row>
     <row r="45" spans="2:10" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B45" s="60"/>
       <c r="C45" s="133"/>
       <c r="D45" s="139"/>
-      <c r="E45" s="79"/>
-      <c r="F45" s="76"/>
-      <c r="G45" s="68"/>
-      <c r="H45" s="75"/>
-      <c r="I45" s="77"/>
-      <c r="J45" s="85"/>
+      <c r="E45" s="78"/>
+      <c r="F45" s="75"/>
+      <c r="G45" s="67"/>
+      <c r="H45" s="74"/>
+      <c r="I45" s="76"/>
+      <c r="J45" s="84"/>
     </row>
     <row r="46" spans="2:10" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B46" s="60"/>
       <c r="C46" s="133"/>
       <c r="D46" s="139"/>
-      <c r="E46" s="79"/>
-      <c r="F46" s="76"/>
-      <c r="G46" s="68"/>
-      <c r="H46" s="75"/>
-      <c r="I46" s="77"/>
-      <c r="J46" s="85"/>
+      <c r="E46" s="78"/>
+      <c r="F46" s="75"/>
+      <c r="G46" s="67"/>
+      <c r="H46" s="74"/>
+      <c r="I46" s="76"/>
+      <c r="J46" s="84"/>
     </row>
     <row r="47" spans="2:10" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B47" s="60"/>
       <c r="C47" s="133"/>
       <c r="D47" s="139"/>
-      <c r="E47" s="79"/>
-      <c r="F47" s="76"/>
-      <c r="G47" s="68"/>
-      <c r="H47" s="75"/>
-      <c r="I47" s="77"/>
-      <c r="J47" s="85"/>
+      <c r="E47" s="78"/>
+      <c r="F47" s="75"/>
+      <c r="G47" s="67"/>
+      <c r="H47" s="74"/>
+      <c r="I47" s="76"/>
+      <c r="J47" s="84"/>
     </row>
     <row r="48" spans="2:10" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B48" s="60"/>
       <c r="C48" s="133"/>
       <c r="D48" s="139"/>
-      <c r="E48" s="79"/>
-      <c r="F48" s="76"/>
-      <c r="G48" s="68"/>
-      <c r="H48" s="75"/>
-      <c r="I48" s="77"/>
-      <c r="J48" s="85"/>
+      <c r="E48" s="78"/>
+      <c r="F48" s="75"/>
+      <c r="G48" s="67"/>
+      <c r="H48" s="74"/>
+      <c r="I48" s="76"/>
+      <c r="J48" s="84"/>
     </row>
     <row r="49" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B49" s="60"/>
       <c r="C49" s="133"/>
       <c r="D49" s="139"/>
-      <c r="E49" s="79"/>
-      <c r="F49" s="76"/>
-      <c r="G49" s="68"/>
-      <c r="H49" s="75"/>
-      <c r="I49" s="75"/>
+      <c r="E49" s="78"/>
+      <c r="F49" s="75"/>
+      <c r="G49" s="67"/>
+      <c r="H49" s="74"/>
+      <c r="I49" s="74"/>
     </row>
     <row r="50" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B50" s="60"/>
       <c r="C50" s="133"/>
       <c r="D50" s="139"/>
-      <c r="E50" s="79"/>
-      <c r="F50" s="76"/>
-      <c r="G50" s="68"/>
-      <c r="H50" s="75"/>
-      <c r="I50" s="75"/>
+      <c r="E50" s="78"/>
+      <c r="F50" s="75"/>
+      <c r="G50" s="67"/>
+      <c r="H50" s="74"/>
+      <c r="I50" s="74"/>
     </row>
     <row r="51" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B51" s="60"/>
       <c r="C51" s="133"/>
       <c r="D51" s="139"/>
-      <c r="E51" s="79"/>
-      <c r="F51" s="76"/>
-      <c r="G51" s="80"/>
-      <c r="H51" s="81"/>
-      <c r="I51" s="75"/>
+      <c r="E51" s="78"/>
+      <c r="F51" s="75"/>
+      <c r="G51" s="79"/>
+      <c r="H51" s="80"/>
+      <c r="I51" s="74"/>
     </row>
     <row r="52" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B52" s="60"/>
       <c r="C52" s="133"/>
       <c r="D52" s="139"/>
-      <c r="E52" s="79"/>
-      <c r="F52" s="76"/>
-      <c r="G52" s="80"/>
-      <c r="H52" s="81"/>
-      <c r="I52" s="75"/>
+      <c r="E52" s="78"/>
+      <c r="F52" s="75"/>
+      <c r="G52" s="79"/>
+      <c r="H52" s="80"/>
+      <c r="I52" s="74"/>
     </row>
     <row r="53" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B53" s="60"/>
       <c r="C53" s="133"/>
       <c r="D53" s="139"/>
-      <c r="E53" s="79"/>
-      <c r="F53" s="76"/>
-      <c r="G53" s="80"/>
-      <c r="H53" s="67"/>
-      <c r="I53" s="75"/>
+      <c r="E53" s="78"/>
+      <c r="F53" s="75"/>
+      <c r="G53" s="79"/>
+      <c r="H53" s="66"/>
+      <c r="I53" s="74"/>
     </row>
     <row r="54" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B54" s="60"/>
       <c r="C54" s="133"/>
       <c r="D54" s="139"/>
-      <c r="E54" s="79"/>
-      <c r="F54" s="76"/>
-      <c r="G54" s="82"/>
-      <c r="H54" s="67"/>
-      <c r="I54" s="75"/>
+      <c r="E54" s="78"/>
+      <c r="F54" s="75"/>
+      <c r="G54" s="81"/>
+      <c r="H54" s="66"/>
+      <c r="I54" s="74"/>
     </row>
     <row r="55" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B55" s="60"/>
       <c r="C55" s="133"/>
       <c r="D55" s="139"/>
-      <c r="E55" s="79"/>
-      <c r="F55" s="76"/>
-      <c r="G55" s="83"/>
-      <c r="H55" s="84"/>
-      <c r="I55" s="75"/>
+      <c r="E55" s="78"/>
+      <c r="F55" s="75"/>
+      <c r="G55" s="82"/>
+      <c r="H55" s="83"/>
+      <c r="I55" s="74"/>
     </row>
     <row r="56" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B56" s="60"/>
       <c r="C56" s="133"/>
       <c r="D56" s="139"/>
-      <c r="E56" s="79"/>
-      <c r="F56" s="76"/>
-      <c r="G56" s="83"/>
-      <c r="H56" s="84"/>
-      <c r="I56" s="75"/>
+      <c r="E56" s="78"/>
+      <c r="F56" s="75"/>
+      <c r="G56" s="82"/>
+      <c r="H56" s="83"/>
+      <c r="I56" s="74"/>
     </row>
     <row r="57" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B57" s="60"/>
       <c r="C57" s="133"/>
       <c r="D57" s="139"/>
-      <c r="E57" s="79"/>
-      <c r="F57" s="76"/>
-      <c r="G57" s="83"/>
-      <c r="H57" s="84"/>
-      <c r="I57" s="75"/>
+      <c r="E57" s="78"/>
+      <c r="F57" s="75"/>
+      <c r="G57" s="82"/>
+      <c r="H57" s="83"/>
+      <c r="I57" s="74"/>
     </row>
     <row r="58" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B58" s="60"/>
       <c r="C58" s="133"/>
       <c r="D58" s="139"/>
-      <c r="E58" s="79"/>
-      <c r="F58" s="76"/>
-      <c r="G58" s="83"/>
-      <c r="H58" s="84"/>
-      <c r="I58" s="75"/>
+      <c r="E58" s="78"/>
+      <c r="F58" s="75"/>
+      <c r="G58" s="82"/>
+      <c r="H58" s="83"/>
+      <c r="I58" s="74"/>
     </row>
     <row r="59" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B59" s="60"/>
       <c r="C59" s="133"/>
       <c r="D59" s="139"/>
-      <c r="E59" s="79"/>
-      <c r="F59" s="76"/>
-      <c r="G59" s="83"/>
-      <c r="H59" s="84"/>
-      <c r="I59" s="75"/>
+      <c r="E59" s="78"/>
+      <c r="F59" s="75"/>
+      <c r="G59" s="82"/>
+      <c r="H59" s="83"/>
+      <c r="I59" s="74"/>
     </row>
     <row r="60" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B60" s="60"/>
       <c r="C60" s="133"/>
       <c r="D60" s="139"/>
-      <c r="E60" s="79"/>
-      <c r="F60" s="76"/>
-      <c r="G60" s="68"/>
-      <c r="H60" s="75"/>
-      <c r="I60" s="75"/>
+      <c r="E60" s="78"/>
+      <c r="F60" s="75"/>
+      <c r="G60" s="67"/>
+      <c r="H60" s="74"/>
+      <c r="I60" s="74"/>
     </row>
     <row r="61" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B61" s="60"/>
       <c r="C61" s="133"/>
       <c r="D61" s="139"/>
-      <c r="E61" s="79"/>
-      <c r="F61" s="76"/>
-      <c r="G61" s="68"/>
-      <c r="H61" s="81"/>
-      <c r="I61" s="75"/>
+      <c r="E61" s="78"/>
+      <c r="F61" s="75"/>
+      <c r="G61" s="67"/>
+      <c r="H61" s="80"/>
+      <c r="I61" s="74"/>
     </row>
     <row r="62" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B62" s="60"/>
       <c r="C62" s="133"/>
       <c r="D62" s="139"/>
-      <c r="E62" s="79"/>
-      <c r="F62" s="76"/>
-      <c r="G62" s="68"/>
-      <c r="H62" s="81"/>
-      <c r="I62" s="75"/>
+      <c r="E62" s="78"/>
+      <c r="F62" s="75"/>
+      <c r="G62" s="67"/>
+      <c r="H62" s="80"/>
+      <c r="I62" s="74"/>
     </row>
     <row r="63" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B63" s="60"/>
       <c r="C63" s="133"/>
       <c r="D63" s="139"/>
-      <c r="E63" s="79"/>
-      <c r="F63" s="76"/>
-      <c r="G63" s="68"/>
-      <c r="H63" s="81"/>
-      <c r="I63" s="75"/>
+      <c r="E63" s="78"/>
+      <c r="F63" s="75"/>
+      <c r="G63" s="67"/>
+      <c r="H63" s="80"/>
+      <c r="I63" s="74"/>
     </row>
     <row r="64" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B64" s="60"/>
       <c r="C64" s="133"/>
       <c r="D64" s="139"/>
-      <c r="E64" s="79"/>
-      <c r="F64" s="76"/>
-      <c r="G64" s="68"/>
-      <c r="H64" s="81"/>
-      <c r="I64" s="75"/>
+      <c r="E64" s="78"/>
+      <c r="F64" s="75"/>
+      <c r="G64" s="67"/>
+      <c r="H64" s="80"/>
+      <c r="I64" s="74"/>
     </row>
     <row r="65" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B65" s="60"/>
       <c r="C65" s="133"/>
       <c r="D65" s="139"/>
-      <c r="E65" s="79"/>
-      <c r="F65" s="76"/>
-      <c r="G65" s="68"/>
-      <c r="H65" s="81"/>
-      <c r="I65" s="75"/>
+      <c r="E65" s="78"/>
+      <c r="F65" s="75"/>
+      <c r="G65" s="67"/>
+      <c r="H65" s="80"/>
+      <c r="I65" s="74"/>
     </row>
     <row r="66" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B66" s="60"/>
       <c r="C66" s="133"/>
       <c r="D66" s="139"/>
-      <c r="E66" s="79"/>
-      <c r="F66" s="76"/>
-      <c r="G66" s="68"/>
-      <c r="H66" s="81"/>
-      <c r="I66" s="75"/>
+      <c r="E66" s="78"/>
+      <c r="F66" s="75"/>
+      <c r="G66" s="67"/>
+      <c r="H66" s="80"/>
+      <c r="I66" s="74"/>
     </row>
     <row r="67" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B67" s="60"/>
       <c r="C67" s="134"/>
       <c r="D67" s="140"/>
-      <c r="E67" s="79"/>
-      <c r="F67" s="86"/>
-      <c r="G67" s="68"/>
-      <c r="H67" s="81"/>
-      <c r="I67" s="75"/>
+      <c r="E67" s="78"/>
+      <c r="F67" s="85"/>
+      <c r="G67" s="67"/>
+      <c r="H67" s="80"/>
+      <c r="I67" s="74"/>
     </row>
     <row r="68" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B68" s="60"/>
       <c r="C68" s="135"/>
       <c r="D68" s="141"/>
-      <c r="E68" s="79"/>
-      <c r="F68" s="87"/>
-      <c r="G68" s="78"/>
-      <c r="H68" s="81"/>
-      <c r="I68" s="75"/>
+      <c r="E68" s="78"/>
+      <c r="F68" s="86"/>
+      <c r="G68" s="77"/>
+      <c r="H68" s="80"/>
+      <c r="I68" s="74"/>
     </row>
     <row r="69" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B69" s="60"/>
       <c r="C69" s="136"/>
       <c r="D69" s="142"/>
-      <c r="E69" s="79"/>
-      <c r="F69" s="87"/>
-      <c r="G69" s="78"/>
-      <c r="H69" s="81"/>
-      <c r="I69" s="75"/>
+      <c r="E69" s="78"/>
+      <c r="F69" s="86"/>
+      <c r="G69" s="77"/>
+      <c r="H69" s="80"/>
+      <c r="I69" s="74"/>
     </row>
     <row r="70" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B70" s="60"/>
       <c r="C70" s="136"/>
       <c r="D70" s="142"/>
-      <c r="E70" s="79"/>
-      <c r="F70" s="87"/>
-      <c r="G70" s="78"/>
-      <c r="H70" s="81"/>
-      <c r="I70" s="75"/>
+      <c r="E70" s="78"/>
+      <c r="F70" s="86"/>
+      <c r="G70" s="77"/>
+      <c r="H70" s="80"/>
+      <c r="I70" s="74"/>
     </row>
     <row r="71" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B71" s="60"/>
       <c r="C71" s="136"/>
       <c r="D71" s="142"/>
-      <c r="E71" s="79"/>
-      <c r="F71" s="87"/>
-      <c r="G71" s="78"/>
-      <c r="H71" s="81"/>
-      <c r="I71" s="75"/>
+      <c r="E71" s="78"/>
+      <c r="F71" s="86"/>
+      <c r="G71" s="77"/>
+      <c r="H71" s="80"/>
+      <c r="I71" s="74"/>
     </row>
     <row r="72" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B72" s="60"/>
       <c r="C72" s="136"/>
       <c r="D72" s="142"/>
-      <c r="E72" s="79"/>
-      <c r="F72" s="88"/>
-      <c r="G72" s="78"/>
-      <c r="H72" s="81"/>
-      <c r="I72" s="75"/>
+      <c r="E72" s="78"/>
+      <c r="F72" s="87"/>
+      <c r="G72" s="77"/>
+      <c r="H72" s="80"/>
+      <c r="I72" s="74"/>
     </row>
     <row r="73" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B73" s="60"/>
       <c r="C73" s="136"/>
       <c r="D73" s="142"/>
-      <c r="E73" s="79"/>
-      <c r="F73" s="88"/>
-      <c r="G73" s="78"/>
-      <c r="H73" s="81"/>
-      <c r="I73" s="75"/>
+      <c r="E73" s="78"/>
+      <c r="F73" s="87"/>
+      <c r="G73" s="77"/>
+      <c r="H73" s="80"/>
+      <c r="I73" s="74"/>
     </row>
     <row r="74" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B74" s="60"/>
       <c r="C74" s="136"/>
       <c r="D74" s="142"/>
-      <c r="E74" s="79"/>
-      <c r="F74" s="88"/>
-      <c r="G74" s="78"/>
-      <c r="H74" s="81"/>
-      <c r="I74" s="75"/>
+      <c r="E74" s="78"/>
+      <c r="F74" s="87"/>
+      <c r="G74" s="77"/>
+      <c r="H74" s="80"/>
+      <c r="I74" s="74"/>
     </row>
     <row r="75" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B75" s="60"/>
       <c r="C75" s="136"/>
       <c r="D75" s="142"/>
-      <c r="E75" s="79"/>
-      <c r="F75" s="76"/>
-      <c r="G75" s="78"/>
-      <c r="H75" s="81"/>
-      <c r="I75" s="75"/>
+      <c r="E75" s="78"/>
+      <c r="F75" s="75"/>
+      <c r="G75" s="77"/>
+      <c r="H75" s="80"/>
+      <c r="I75" s="74"/>
     </row>
     <row r="76" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B76" s="60"/>
       <c r="C76" s="136"/>
       <c r="D76" s="142"/>
-      <c r="E76" s="79"/>
-      <c r="F76" s="86"/>
-      <c r="G76" s="78"/>
-      <c r="H76" s="81"/>
-      <c r="I76" s="75"/>
+      <c r="E76" s="78"/>
+      <c r="F76" s="85"/>
+      <c r="G76" s="77"/>
+      <c r="H76" s="80"/>
+      <c r="I76" s="74"/>
     </row>
     <row r="77" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B77" s="60"/>
       <c r="C77" s="136"/>
       <c r="D77" s="142"/>
-      <c r="E77" s="79"/>
-      <c r="F77" s="87"/>
-      <c r="G77" s="78"/>
-      <c r="H77" s="81"/>
-      <c r="I77" s="75"/>
+      <c r="E77" s="78"/>
+      <c r="F77" s="86"/>
+      <c r="G77" s="77"/>
+      <c r="H77" s="80"/>
+      <c r="I77" s="74"/>
     </row>
     <row r="78" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B78" s="60"/>
       <c r="C78" s="136"/>
       <c r="D78" s="142"/>
-      <c r="E78" s="79"/>
-      <c r="F78" s="87"/>
-      <c r="G78" s="78"/>
-      <c r="H78" s="81"/>
-      <c r="I78" s="75"/>
+      <c r="E78" s="78"/>
+      <c r="F78" s="86"/>
+      <c r="G78" s="77"/>
+      <c r="H78" s="80"/>
+      <c r="I78" s="74"/>
     </row>
     <row r="79" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B79" s="60"/>
       <c r="C79" s="136"/>
       <c r="D79" s="142"/>
-      <c r="E79" s="79"/>
-      <c r="F79" s="87"/>
-      <c r="G79" s="78"/>
-      <c r="H79" s="81"/>
-      <c r="I79" s="75"/>
+      <c r="E79" s="78"/>
+      <c r="F79" s="86"/>
+      <c r="G79" s="77"/>
+      <c r="H79" s="80"/>
+      <c r="I79" s="74"/>
     </row>
     <row r="80" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B80" s="60"/>
       <c r="C80" s="136"/>
       <c r="D80" s="142"/>
-      <c r="E80" s="79"/>
-      <c r="F80" s="87"/>
-      <c r="G80" s="78"/>
-      <c r="H80" s="81"/>
-      <c r="I80" s="75"/>
+      <c r="E80" s="78"/>
+      <c r="F80" s="86"/>
+      <c r="G80" s="77"/>
+      <c r="H80" s="80"/>
+      <c r="I80" s="74"/>
     </row>
     <row r="81" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B81" s="60"/>
       <c r="C81" s="136"/>
       <c r="D81" s="142"/>
-      <c r="E81" s="79"/>
-      <c r="F81" s="88"/>
-      <c r="G81" s="78"/>
-      <c r="H81" s="81"/>
-      <c r="I81" s="75"/>
+      <c r="E81" s="78"/>
+      <c r="F81" s="87"/>
+      <c r="G81" s="77"/>
+      <c r="H81" s="80"/>
+      <c r="I81" s="74"/>
     </row>
     <row r="82" spans="2:9" ht="30" customHeight="1">
       <c r="B82" s="60"/>
       <c r="C82" s="136"/>
       <c r="D82" s="142"/>
-      <c r="E82" s="79"/>
-      <c r="F82" s="88"/>
-      <c r="G82" s="78"/>
-      <c r="H82" s="89"/>
-      <c r="I82" s="75"/>
+      <c r="E82" s="78"/>
+      <c r="F82" s="87"/>
+      <c r="G82" s="77"/>
+      <c r="H82" s="88"/>
+      <c r="I82" s="74"/>
     </row>
     <row r="83" spans="2:9" ht="30" customHeight="1">
       <c r="B83" s="60"/>
       <c r="C83" s="136"/>
       <c r="D83" s="142"/>
-      <c r="E83" s="79"/>
-      <c r="F83" s="88"/>
-      <c r="G83" s="78"/>
-      <c r="H83" s="89"/>
-      <c r="I83" s="75"/>
+      <c r="E83" s="78"/>
+      <c r="F83" s="87"/>
+      <c r="G83" s="77"/>
+      <c r="H83" s="88"/>
+      <c r="I83" s="74"/>
     </row>
     <row r="84" spans="2:9" ht="30" customHeight="1">
       <c r="B84" s="60"/>
       <c r="C84" s="136"/>
       <c r="D84" s="142"/>
-      <c r="E84" s="79"/>
-      <c r="F84" s="88"/>
-      <c r="G84" s="78"/>
-      <c r="H84" s="89"/>
-      <c r="I84" s="75"/>
+      <c r="E84" s="78"/>
+      <c r="F84" s="87"/>
+      <c r="G84" s="77"/>
+      <c r="H84" s="88"/>
+      <c r="I84" s="74"/>
     </row>
     <row r="85" spans="2:9" ht="30" customHeight="1">
       <c r="B85" s="60"/>
       <c r="C85" s="136"/>
       <c r="D85" s="142"/>
-      <c r="E85" s="79"/>
-      <c r="F85" s="88"/>
-      <c r="G85" s="78"/>
-      <c r="H85" s="89"/>
-      <c r="I85" s="75"/>
+      <c r="E85" s="78"/>
+      <c r="F85" s="87"/>
+      <c r="G85" s="77"/>
+      <c r="H85" s="88"/>
+      <c r="I85" s="74"/>
     </row>
     <row r="86" spans="2:9" ht="30" customHeight="1">
       <c r="B86" s="60"/>
       <c r="C86" s="136"/>
       <c r="D86" s="142"/>
-      <c r="E86" s="79"/>
-      <c r="F86" s="88"/>
-      <c r="G86" s="78"/>
-      <c r="H86" s="89"/>
-      <c r="I86" s="75"/>
+      <c r="E86" s="78"/>
+      <c r="F86" s="87"/>
+      <c r="G86" s="77"/>
+      <c r="H86" s="88"/>
+      <c r="I86" s="74"/>
     </row>
     <row r="87" spans="2:9" ht="30" customHeight="1">
       <c r="B87" s="60"/>
       <c r="C87" s="137"/>
       <c r="D87" s="143"/>
-      <c r="E87" s="79"/>
-      <c r="F87" s="88"/>
-      <c r="G87" s="78"/>
-      <c r="H87" s="89"/>
-      <c r="I87" s="75"/>
+      <c r="E87" s="78"/>
+      <c r="F87" s="87"/>
+      <c r="G87" s="77"/>
+      <c r="H87" s="88"/>
+      <c r="I87" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -3414,90 +3580,90 @@
       <c r="L5" s="48"/>
       <c r="M5" s="48"/>
     </row>
-    <row r="6" spans="2:13" s="27" customFormat="1" ht="50" customHeight="1">
-      <c r="B6" s="35">
+    <row r="6" spans="2:13" ht="50" customHeight="1">
+      <c r="B6" s="159">
         <v>1</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="C6" s="160" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="37" t="s">
+      <c r="D6" s="161" t="s">
         <v>66</v>
       </c>
-      <c r="E6" s="42">
+      <c r="E6" s="162">
         <v>44543</v>
       </c>
-      <c r="F6" s="43">
+      <c r="F6" s="163">
         <v>44548</v>
       </c>
-      <c r="G6" s="44">
+      <c r="G6" s="164">
         <f t="shared" ref="G6:G8" si="0">F6-E6</f>
         <v>5</v>
       </c>
-      <c r="H6" s="43">
+      <c r="H6" s="163">
         <v>44562</v>
       </c>
-      <c r="I6" s="44">
+      <c r="I6" s="164">
         <f>H6-E6</f>
         <v>19</v>
       </c>
-      <c r="J6" s="49" t="s">
+      <c r="J6" s="165" t="s">
         <v>67</v>
       </c>
-      <c r="K6" s="48"/>
-      <c r="L6" s="48"/>
-    </row>
-    <row r="7" spans="2:13" s="27" customFormat="1" ht="50" customHeight="1">
-      <c r="B7" s="35">
+      <c r="K6" s="52"/>
+      <c r="L6" s="52"/>
+    </row>
+    <row r="7" spans="2:13" ht="50" customHeight="1">
+      <c r="B7" s="159">
         <v>2</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="160" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="37" t="s">
+      <c r="D7" s="161" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="42">
+      <c r="E7" s="162">
         <v>44549</v>
       </c>
-      <c r="F7" s="43">
+      <c r="F7" s="163">
         <v>44559</v>
       </c>
-      <c r="G7" s="44">
+      <c r="G7" s="164">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="H7" s="43"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="49"/>
-      <c r="K7" s="48"/>
-      <c r="L7" s="48"/>
-    </row>
-    <row r="8" spans="2:13" s="27" customFormat="1" ht="50" customHeight="1">
-      <c r="B8" s="35">
+      <c r="H7" s="163"/>
+      <c r="I7" s="164"/>
+      <c r="J7" s="165"/>
+      <c r="K7" s="52"/>
+      <c r="L7" s="52"/>
+    </row>
+    <row r="8" spans="2:13" ht="50" customHeight="1">
+      <c r="B8" s="159">
         <v>3</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="160" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="37" t="s">
+      <c r="D8" s="161" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="42">
+      <c r="E8" s="162">
         <v>44560</v>
       </c>
-      <c r="F8" s="43">
+      <c r="F8" s="163">
         <v>44565</v>
       </c>
-      <c r="G8" s="44">
+      <c r="G8" s="164">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="H8" s="43"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="49"/>
-      <c r="K8" s="48"/>
-      <c r="L8" s="48"/>
+      <c r="H8" s="163"/>
+      <c r="I8" s="164"/>
+      <c r="J8" s="165"/>
+      <c r="K8" s="52"/>
+      <c r="L8" s="52"/>
     </row>
     <row r="9" spans="2:13" s="27" customFormat="1" ht="50" customHeight="1">
       <c r="B9" s="35"/>
@@ -6208,7 +6374,7 @@
       <c r="K8" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="L8" s="104" t="s">
+      <c r="L8" s="103" t="s">
         <v>233</v>
       </c>
       <c r="M8" s="12" t="s">
@@ -7597,57 +7763,81 @@
       <c r="H3" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="I3" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="J3" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="K3" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="L3" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="M3" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="N3" s="90" t="s">
+      <c r="I3" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="J3" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="K3" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="L3" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="M3" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="N3" s="89" t="s">
         <v>216</v>
       </c>
-      <c r="O3" s="90" t="s">
+      <c r="O3" s="89" t="s">
         <v>216</v>
       </c>
-      <c r="P3" s="90" t="s">
+      <c r="P3" s="89" t="s">
         <v>216</v>
       </c>
-      <c r="Q3" s="90" t="s">
+      <c r="Q3" s="89" t="s">
         <v>216</v>
       </c>
-      <c r="R3" s="90" t="s">
+      <c r="R3" s="89" t="s">
         <v>216</v>
       </c>
-      <c r="S3" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="T3" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="U3" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="V3" s="12"/>
-      <c r="W3" s="12"/>
-      <c r="X3" s="12"/>
-      <c r="Y3" s="12"/>
-      <c r="Z3" s="12"/>
-      <c r="AA3" s="12"/>
-      <c r="AB3" s="12"/>
-      <c r="AC3" s="12"/>
-      <c r="AD3" s="12"/>
-      <c r="AE3" s="15"/>
-      <c r="AF3" s="15"/>
-      <c r="AG3" s="15"/>
+      <c r="S3" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="T3" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="U3" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="V3" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="W3" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="X3" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y3" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z3" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA3" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB3" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC3" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AD3" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AE3" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AF3" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AG3" s="89" t="s">
+        <v>215</v>
+      </c>
       <c r="AH3" s="15"/>
       <c r="AI3" s="12" t="s">
         <v>216</v>
@@ -7671,57 +7861,81 @@
       <c r="H4" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="I4" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="J4" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="K4" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="L4" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="M4" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="N4" s="90" t="s">
+      <c r="I4" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="J4" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="K4" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="L4" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="M4" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="N4" s="89" t="s">
         <v>216</v>
       </c>
-      <c r="O4" s="90" t="s">
+      <c r="O4" s="89" t="s">
         <v>216</v>
       </c>
-      <c r="P4" s="90" t="s">
+      <c r="P4" s="89" t="s">
         <v>216</v>
       </c>
-      <c r="Q4" s="90" t="s">
+      <c r="Q4" s="89" t="s">
         <v>216</v>
       </c>
-      <c r="R4" s="90" t="s">
+      <c r="R4" s="89" t="s">
         <v>216</v>
       </c>
-      <c r="S4" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="T4" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="U4" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="V4" s="12"/>
-      <c r="W4" s="12"/>
-      <c r="X4" s="12"/>
-      <c r="Y4" s="12"/>
-      <c r="Z4" s="12"/>
-      <c r="AA4" s="12"/>
-      <c r="AB4" s="12"/>
-      <c r="AC4" s="12"/>
-      <c r="AD4" s="12"/>
-      <c r="AE4" s="15"/>
-      <c r="AF4" s="15"/>
-      <c r="AG4" s="15"/>
+      <c r="S4" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="T4" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="U4" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="V4" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="W4" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="X4" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y4" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z4" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA4" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB4" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC4" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AD4" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AE4" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AF4" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AG4" s="89" t="s">
+        <v>215</v>
+      </c>
       <c r="AH4" s="15"/>
     </row>
     <row r="5" spans="1:35" ht="21" customHeight="1">
@@ -7748,57 +7962,81 @@
       <c r="H5" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="I5" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="J5" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="K5" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="L5" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="M5" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="N5" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="O5" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="P5" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q5" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="R5" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="S5" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="T5" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="U5" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="V5" s="12"/>
-      <c r="W5" s="12"/>
-      <c r="X5" s="12"/>
-      <c r="Y5" s="12"/>
-      <c r="Z5" s="12"/>
-      <c r="AA5" s="12"/>
-      <c r="AB5" s="12"/>
-      <c r="AC5" s="12"/>
-      <c r="AD5" s="12"/>
-      <c r="AE5" s="15"/>
-      <c r="AF5" s="15"/>
-      <c r="AG5" s="15"/>
+      <c r="I5" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="J5" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="K5" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="L5" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="M5" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="N5" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="O5" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="P5" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q5" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="R5" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="S5" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="T5" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="U5" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="V5" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="W5" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="X5" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y5" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z5" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA5" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB5" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC5" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AD5" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AE5" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AF5" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AG5" s="89" t="s">
+        <v>215</v>
+      </c>
       <c r="AH5" s="15"/>
     </row>
     <row r="6" spans="1:35" ht="23" customHeight="1">
@@ -7821,57 +8059,81 @@
       <c r="H6" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="I6" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="J6" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="K6" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="L6" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="M6" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="N6" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="O6" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="P6" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q6" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="R6" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="S6" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="T6" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="U6" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="V6" s="12"/>
-      <c r="W6" s="12"/>
-      <c r="X6" s="12"/>
-      <c r="Y6" s="12"/>
-      <c r="Z6" s="12"/>
-      <c r="AA6" s="12"/>
-      <c r="AB6" s="12"/>
-      <c r="AC6" s="12"/>
-      <c r="AD6" s="12"/>
-      <c r="AE6" s="15"/>
-      <c r="AF6" s="15"/>
-      <c r="AG6" s="15"/>
+      <c r="I6" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="J6" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="K6" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="L6" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="M6" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="N6" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="O6" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="P6" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q6" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="R6" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="S6" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="T6" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="U6" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="V6" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="W6" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="X6" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y6" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z6" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA6" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB6" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC6" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AD6" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AE6" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AF6" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AG6" s="89" t="s">
+        <v>215</v>
+      </c>
       <c r="AH6" s="15"/>
     </row>
     <row r="7" spans="1:35" ht="18">
@@ -7898,57 +8160,81 @@
       <c r="H7" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="I7" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="J7" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="K7" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="L7" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="M7" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="N7" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="O7" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="P7" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q7" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="R7" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="S7" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="T7" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="U7" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="V7" s="12"/>
-      <c r="W7" s="12"/>
-      <c r="X7" s="12"/>
-      <c r="Y7" s="12"/>
-      <c r="Z7" s="12"/>
-      <c r="AA7" s="12"/>
-      <c r="AB7" s="12"/>
-      <c r="AC7" s="12"/>
-      <c r="AD7" s="12"/>
-      <c r="AE7" s="15"/>
-      <c r="AF7" s="15"/>
-      <c r="AG7" s="15"/>
+      <c r="I7" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="J7" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="K7" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="L7" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="M7" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="N7" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="O7" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="P7" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q7" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="R7" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="S7" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="T7" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="U7" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="V7" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="W7" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="X7" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y7" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z7" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA7" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB7" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC7" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AD7" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AE7" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AF7" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AG7" s="89" t="s">
+        <v>215</v>
+      </c>
       <c r="AH7" s="15"/>
     </row>
     <row r="8" spans="1:35" ht="18">
@@ -7969,57 +8255,81 @@
       <c r="H8" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="I8" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="J8" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="K8" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="L8" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="M8" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="N8" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="O8" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="P8" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q8" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="R8" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="S8" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="T8" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="U8" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="V8" s="12"/>
-      <c r="W8" s="12"/>
-      <c r="X8" s="12"/>
-      <c r="Y8" s="12"/>
-      <c r="Z8" s="12"/>
-      <c r="AA8" s="12"/>
-      <c r="AB8" s="12"/>
-      <c r="AC8" s="12"/>
-      <c r="AD8" s="12"/>
-      <c r="AE8" s="15"/>
-      <c r="AF8" s="15"/>
-      <c r="AG8" s="15"/>
+      <c r="I8" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="J8" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="K8" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="L8" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="M8" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="N8" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="O8" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="P8" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q8" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="R8" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="S8" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="T8" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="U8" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="V8" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="W8" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="X8" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y8" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z8" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA8" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB8" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC8" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AD8" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AE8" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AF8" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AG8" s="89" t="s">
+        <v>215</v>
+      </c>
       <c r="AH8" s="15"/>
     </row>
     <row r="9" spans="1:35" ht="18">
@@ -8046,57 +8356,81 @@
       <c r="H9" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="I9" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="J9" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="K9" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="L9" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="M9" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="N9" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="O9" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="P9" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q9" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="R9" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="S9" s="90" t="s">
+      <c r="I9" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="J9" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="K9" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="L9" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="M9" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="N9" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="O9" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="P9" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q9" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="R9" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="S9" s="89" t="s">
         <v>216</v>
       </c>
-      <c r="T9" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="U9" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="V9" s="12"/>
-      <c r="W9" s="12"/>
-      <c r="X9" s="12"/>
-      <c r="Y9" s="12"/>
-      <c r="Z9" s="12"/>
-      <c r="AA9" s="12"/>
-      <c r="AB9" s="12"/>
-      <c r="AC9" s="12"/>
-      <c r="AD9" s="12"/>
-      <c r="AE9" s="15"/>
-      <c r="AF9" s="15"/>
-      <c r="AG9" s="15"/>
+      <c r="T9" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="U9" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="V9" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="W9" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="X9" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y9" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z9" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA9" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB9" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC9" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AD9" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AE9" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AF9" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AG9" s="89" t="s">
+        <v>215</v>
+      </c>
       <c r="AH9" s="15"/>
     </row>
     <row r="10" spans="1:35" ht="18">
@@ -8117,57 +8451,81 @@
       <c r="H10" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="I10" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="J10" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="K10" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="L10" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="M10" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="N10" s="90" t="s">
+      <c r="I10" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="J10" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="K10" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="L10" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="M10" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="N10" s="89" t="s">
         <v>216</v>
       </c>
-      <c r="O10" s="90" t="s">
+      <c r="O10" s="89" t="s">
         <v>216</v>
       </c>
-      <c r="P10" s="90" t="s">
+      <c r="P10" s="89" t="s">
         <v>216</v>
       </c>
-      <c r="Q10" s="90" t="s">
+      <c r="Q10" s="89" t="s">
         <v>216</v>
       </c>
-      <c r="R10" s="90" t="s">
+      <c r="R10" s="89" t="s">
         <v>216</v>
       </c>
-      <c r="S10" s="90" t="s">
+      <c r="S10" s="89" t="s">
         <v>216</v>
       </c>
-      <c r="T10" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="U10" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="V10" s="12"/>
-      <c r="W10" s="12"/>
-      <c r="X10" s="12"/>
-      <c r="Y10" s="12"/>
-      <c r="Z10" s="12"/>
-      <c r="AA10" s="12"/>
-      <c r="AB10" s="12"/>
-      <c r="AC10" s="12"/>
-      <c r="AD10" s="12"/>
-      <c r="AE10" s="15"/>
-      <c r="AF10" s="15"/>
-      <c r="AG10" s="15"/>
+      <c r="T10" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="U10" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="V10" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="W10" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="X10" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y10" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z10" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA10" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB10" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC10" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AD10" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AE10" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AF10" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AG10" s="89" t="s">
+        <v>215</v>
+      </c>
       <c r="AH10" s="15"/>
     </row>
     <row r="11" spans="1:35" ht="18">
@@ -8188,57 +8546,81 @@
       <c r="H11" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="I11" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="J11" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="K11" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="L11" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="M11" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="N11" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="O11" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="P11" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q11" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="R11" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="S11" s="90" t="s">
+      <c r="I11" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="J11" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="K11" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="L11" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="M11" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="N11" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="O11" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="P11" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q11" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="R11" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="S11" s="89" t="s">
         <v>216</v>
       </c>
-      <c r="T11" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="U11" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="V11" s="12"/>
-      <c r="W11" s="12"/>
-      <c r="X11" s="12"/>
-      <c r="Y11" s="12"/>
-      <c r="Z11" s="12"/>
-      <c r="AA11" s="12"/>
-      <c r="AB11" s="12"/>
-      <c r="AC11" s="12"/>
-      <c r="AD11" s="12"/>
-      <c r="AE11" s="15"/>
-      <c r="AF11" s="15"/>
-      <c r="AG11" s="15"/>
+      <c r="T11" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="U11" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="V11" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="W11" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="X11" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y11" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z11" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA11" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB11" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC11" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AD11" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AE11" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AF11" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AG11" s="89" t="s">
+        <v>215</v>
+      </c>
       <c r="AH11" s="15"/>
     </row>
     <row r="12" spans="1:35" ht="18">
@@ -8265,57 +8647,81 @@
       <c r="H12" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="I12" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="J12" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="K12" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="L12" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="M12" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="N12" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="O12" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="P12" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q12" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="R12" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="S12" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="T12" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="U12" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="V12" s="12"/>
-      <c r="W12" s="12"/>
-      <c r="X12" s="12"/>
-      <c r="Y12" s="12"/>
-      <c r="Z12" s="12"/>
-      <c r="AA12" s="12"/>
-      <c r="AB12" s="12"/>
-      <c r="AC12" s="12"/>
-      <c r="AD12" s="12"/>
-      <c r="AE12" s="15"/>
-      <c r="AF12" s="15"/>
-      <c r="AG12" s="15"/>
+      <c r="I12" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="J12" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="K12" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="L12" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="M12" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="N12" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="O12" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="P12" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q12" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="R12" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="S12" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="T12" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="U12" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="V12" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="W12" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="X12" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y12" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z12" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA12" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB12" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC12" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AD12" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AE12" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AF12" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AG12" s="89" t="s">
+        <v>215</v>
+      </c>
       <c r="AH12" s="15"/>
     </row>
     <row r="13" spans="1:35" ht="18">
@@ -8336,57 +8742,81 @@
       <c r="H13" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="I13" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="J13" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="K13" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="L13" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="M13" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="N13" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="O13" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="P13" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q13" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="R13" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="S13" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="T13" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="U13" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="V13" s="12"/>
-      <c r="W13" s="12"/>
-      <c r="X13" s="12"/>
-      <c r="Y13" s="12"/>
-      <c r="Z13" s="12"/>
-      <c r="AA13" s="12"/>
-      <c r="AB13" s="12"/>
-      <c r="AC13" s="12"/>
-      <c r="AD13" s="12"/>
-      <c r="AE13" s="15"/>
-      <c r="AF13" s="15"/>
-      <c r="AG13" s="15"/>
+      <c r="I13" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="J13" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="K13" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="L13" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="M13" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="N13" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="O13" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="P13" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q13" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="R13" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="S13" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="T13" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="U13" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="V13" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="W13" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="X13" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y13" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z13" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA13" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB13" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC13" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AD13" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AE13" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AF13" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AG13" s="89" t="s">
+        <v>215</v>
+      </c>
       <c r="AH13" s="15"/>
     </row>
     <row r="14" spans="1:35" ht="18">
@@ -8413,57 +8843,81 @@
       <c r="H14" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="I14" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="J14" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="K14" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="L14" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="M14" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="N14" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="O14" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="P14" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q14" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="R14" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="S14" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="T14" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="U14" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="V14" s="12"/>
-      <c r="W14" s="12"/>
-      <c r="X14" s="12"/>
-      <c r="Y14" s="12"/>
-      <c r="Z14" s="12"/>
-      <c r="AA14" s="12"/>
-      <c r="AB14" s="12"/>
-      <c r="AC14" s="12"/>
-      <c r="AD14" s="12"/>
-      <c r="AE14" s="15"/>
-      <c r="AF14" s="15"/>
-      <c r="AG14" s="15"/>
+      <c r="I14" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="J14" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="K14" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="L14" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="M14" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="N14" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="O14" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="P14" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q14" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="R14" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="S14" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="T14" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="U14" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="V14" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="W14" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="X14" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y14" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z14" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA14" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB14" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC14" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AD14" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AE14" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AF14" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AG14" s="89" t="s">
+        <v>215</v>
+      </c>
       <c r="AH14" s="15"/>
     </row>
     <row r="15" spans="1:35" ht="30">
@@ -8490,57 +8944,81 @@
       <c r="H15" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="I15" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="J15" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="K15" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="L15" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="M15" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="N15" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="O15" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="P15" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q15" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="R15" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="S15" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="T15" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="U15" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="V15" s="14"/>
-      <c r="W15" s="14"/>
-      <c r="X15" s="14"/>
-      <c r="Y15" s="14"/>
-      <c r="Z15" s="14"/>
-      <c r="AA15" s="14"/>
-      <c r="AB15" s="14"/>
-      <c r="AC15" s="14"/>
-      <c r="AD15" s="14"/>
-      <c r="AE15" s="14"/>
-      <c r="AF15" s="14"/>
-      <c r="AG15" s="14"/>
+      <c r="I15" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="J15" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="K15" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="L15" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="M15" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="N15" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="O15" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="P15" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q15" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="R15" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="S15" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="T15" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="U15" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="V15" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="W15" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="X15" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y15" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z15" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA15" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB15" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC15" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AD15" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AE15" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AF15" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AG15" s="89" t="s">
+        <v>215</v>
+      </c>
       <c r="AH15" s="14"/>
     </row>
     <row r="16" spans="1:35" ht="18">
@@ -8561,57 +9039,81 @@
       <c r="H16" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="I16" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="J16" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="K16" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="L16" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="M16" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="N16" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="O16" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="P16" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q16" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="R16" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="S16" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="T16" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="U16" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="V16" s="14"/>
-      <c r="W16" s="14"/>
-      <c r="X16" s="14"/>
-      <c r="Y16" s="14"/>
-      <c r="Z16" s="14"/>
-      <c r="AA16" s="14"/>
-      <c r="AB16" s="14"/>
-      <c r="AC16" s="14"/>
-      <c r="AD16" s="14"/>
-      <c r="AE16" s="14"/>
-      <c r="AF16" s="14"/>
-      <c r="AG16" s="14"/>
+      <c r="I16" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="J16" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="K16" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="L16" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="M16" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="N16" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="O16" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="P16" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q16" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="R16" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="S16" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="T16" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="U16" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="V16" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="W16" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="X16" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y16" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z16" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA16" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB16" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC16" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AD16" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AE16" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AF16" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AG16" s="89" t="s">
+        <v>215</v>
+      </c>
       <c r="AH16" s="14"/>
     </row>
     <row r="17" spans="1:34" ht="18">
@@ -8632,57 +9134,81 @@
       <c r="H17" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="I17" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="J17" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="K17" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="L17" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="M17" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="N17" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="O17" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="P17" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q17" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="R17" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="S17" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="T17" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="U17" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="V17" s="14"/>
-      <c r="W17" s="14"/>
-      <c r="X17" s="14"/>
-      <c r="Y17" s="14"/>
-      <c r="Z17" s="14"/>
-      <c r="AA17" s="14"/>
-      <c r="AB17" s="14"/>
-      <c r="AC17" s="14"/>
-      <c r="AD17" s="14"/>
-      <c r="AE17" s="14"/>
-      <c r="AF17" s="14"/>
-      <c r="AG17" s="14"/>
+      <c r="I17" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="J17" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="K17" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="L17" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="M17" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="N17" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="O17" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="P17" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q17" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="R17" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="S17" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="T17" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="U17" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="V17" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="W17" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="X17" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y17" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z17" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA17" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB17" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC17" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AD17" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AE17" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AF17" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AG17" s="89" t="s">
+        <v>215</v>
+      </c>
       <c r="AH17" s="14"/>
     </row>
     <row r="18" spans="1:34" ht="18">
@@ -8703,57 +9229,81 @@
       <c r="H18" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="I18" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="J18" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="K18" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="L18" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="M18" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="N18" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="O18" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="P18" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q18" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="R18" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="S18" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="T18" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="U18" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="V18" s="14"/>
-      <c r="W18" s="14"/>
-      <c r="X18" s="14"/>
-      <c r="Y18" s="14"/>
-      <c r="Z18" s="14"/>
-      <c r="AA18" s="14"/>
-      <c r="AB18" s="14"/>
-      <c r="AC18" s="14"/>
-      <c r="AD18" s="14"/>
-      <c r="AE18" s="14"/>
-      <c r="AF18" s="14"/>
-      <c r="AG18" s="14"/>
+      <c r="I18" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="J18" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="K18" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="L18" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="M18" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="N18" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="O18" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="P18" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q18" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="R18" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="S18" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="T18" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="U18" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="V18" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="W18" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="X18" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y18" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z18" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA18" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB18" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC18" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AD18" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AE18" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AF18" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AG18" s="89" t="s">
+        <v>215</v>
+      </c>
       <c r="AH18" s="14"/>
     </row>
     <row r="19" spans="1:34" ht="18">
@@ -8780,57 +9330,81 @@
       <c r="H19" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="I19" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="J19" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="K19" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="L19" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="M19" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="N19" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="O19" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="P19" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q19" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="R19" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="S19" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="T19" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="U19" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="V19" s="14"/>
-      <c r="W19" s="14"/>
-      <c r="X19" s="14"/>
-      <c r="Y19" s="14"/>
-      <c r="Z19" s="14"/>
-      <c r="AA19" s="14"/>
-      <c r="AB19" s="14"/>
-      <c r="AC19" s="14"/>
-      <c r="AD19" s="14"/>
-      <c r="AE19" s="14"/>
-      <c r="AF19" s="14"/>
-      <c r="AG19" s="14"/>
+      <c r="I19" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="J19" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="K19" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="L19" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="M19" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="N19" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="O19" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="P19" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q19" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="R19" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="S19" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="T19" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="U19" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="V19" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="W19" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="X19" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y19" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z19" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA19" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB19" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC19" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AD19" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AE19" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AF19" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AG19" s="89" t="s">
+        <v>215</v>
+      </c>
       <c r="AH19" s="14"/>
     </row>
     <row r="20" spans="1:34" ht="18">
@@ -8851,57 +9425,81 @@
       <c r="H20" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="I20" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="J20" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="K20" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="L20" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="M20" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="N20" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="O20" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="P20" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q20" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="R20" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="S20" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="T20" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="U20" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="V20" s="14"/>
-      <c r="W20" s="14"/>
-      <c r="X20" s="14"/>
-      <c r="Y20" s="14"/>
-      <c r="Z20" s="14"/>
-      <c r="AA20" s="14"/>
-      <c r="AB20" s="14"/>
-      <c r="AC20" s="14"/>
-      <c r="AD20" s="14"/>
-      <c r="AE20" s="14"/>
-      <c r="AF20" s="14"/>
-      <c r="AG20" s="14"/>
+      <c r="I20" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="J20" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="K20" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="L20" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="M20" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="N20" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="O20" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="P20" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q20" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="R20" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="S20" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="T20" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="U20" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="V20" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="W20" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="X20" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y20" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z20" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA20" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB20" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC20" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AD20" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AE20" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AF20" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AG20" s="89" t="s">
+        <v>215</v>
+      </c>
       <c r="AH20" s="14"/>
     </row>
     <row r="21" spans="1:34" ht="18">
@@ -8922,108 +9520,156 @@
       <c r="H21" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="I21" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="J21" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="K21" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="L21" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="M21" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="N21" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="O21" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="P21" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q21" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="R21" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="S21" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="T21" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="U21" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="V21" s="14"/>
-      <c r="W21" s="14"/>
-      <c r="X21" s="14"/>
-      <c r="Y21" s="14"/>
-      <c r="Z21" s="14"/>
-      <c r="AA21" s="14"/>
-      <c r="AB21" s="14"/>
-      <c r="AC21" s="14"/>
-      <c r="AD21" s="14"/>
-      <c r="AE21" s="14"/>
-      <c r="AF21" s="14"/>
-      <c r="AG21" s="14"/>
+      <c r="I21" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="J21" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="K21" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="L21" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="M21" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="N21" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="O21" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="P21" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q21" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="R21" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="S21" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="T21" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="U21" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="V21" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="W21" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="X21" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y21" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z21" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA21" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB21" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC21" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AD21" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AE21" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AF21" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AG21" s="89" t="s">
+        <v>215</v>
+      </c>
       <c r="AH21" s="14"/>
     </row>
     <row r="22" spans="1:34" ht="18">
-      <c r="A22" s="105">
+      <c r="A22" s="104">
         <v>9</v>
       </c>
-      <c r="B22" s="105" t="s">
+      <c r="B22" s="104" t="s">
         <v>241</v>
       </c>
-      <c r="C22" s="105" t="s">
+      <c r="C22" s="104" t="s">
         <v>242</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="E22" s="105"/>
+      <c r="E22" s="104"/>
       <c r="F22" s="11">
         <f>COUNTIF(G22:AH22,$AI$3)/15</f>
         <v>0.13333333333333333</v>
       </c>
       <c r="G22" s="22"/>
-      <c r="H22" s="106"/>
-      <c r="I22" s="106"/>
-      <c r="J22" s="106"/>
-      <c r="K22" s="106"/>
-      <c r="L22" s="106"/>
-      <c r="M22" s="106"/>
-      <c r="N22" s="106"/>
-      <c r="O22" s="106"/>
-      <c r="P22" s="106"/>
-      <c r="Q22" s="106"/>
-      <c r="R22" s="106"/>
-      <c r="S22" s="106"/>
-      <c r="T22" s="90" t="s">
+      <c r="H22" s="105"/>
+      <c r="I22" s="105"/>
+      <c r="J22" s="105"/>
+      <c r="K22" s="105"/>
+      <c r="L22" s="105"/>
+      <c r="M22" s="105"/>
+      <c r="N22" s="105"/>
+      <c r="O22" s="105"/>
+      <c r="P22" s="105"/>
+      <c r="Q22" s="105"/>
+      <c r="R22" s="105"/>
+      <c r="S22" s="105"/>
+      <c r="T22" s="89" t="s">
         <v>216</v>
       </c>
-      <c r="U22" s="90" t="s">
+      <c r="U22" s="89" t="s">
         <v>216</v>
       </c>
-      <c r="V22" s="15"/>
-      <c r="W22" s="15"/>
-      <c r="X22" s="15"/>
-      <c r="Y22" s="15"/>
-      <c r="Z22" s="15"/>
-      <c r="AA22" s="15"/>
-      <c r="AB22" s="15"/>
-      <c r="AC22" s="15"/>
-      <c r="AD22" s="15"/>
-      <c r="AE22" s="15"/>
-      <c r="AF22" s="15"/>
-      <c r="AG22" s="15"/>
+      <c r="V22" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="W22" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="X22" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y22" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z22" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA22" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB22" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC22" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AD22" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AE22" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AF22" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="AG22" s="89" t="s">
+        <v>215</v>
+      </c>
       <c r="AH22" s="15"/>
     </row>
   </sheetData>

--- a/年度计划表.xlsx
+++ b/年度计划表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kayla/Desktop/Workspace/kayla00822.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D6DD98-CFB5-0F49-8DC6-A7171D0E2168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B3869D-96EF-6E49-B541-3E774639D1F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1540" yWindow="8120" windowWidth="14400" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2022书单表" sheetId="2" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="2022年度计划表" sheetId="1" r:id="rId5"/>
     <sheet name="1月计划表" sheetId="7" r:id="rId6"/>
     <sheet name="2月计划表" sheetId="8" r:id="rId7"/>
+    <sheet name="3月计划表" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1455" uniqueCount="256">
   <si>
     <t>序号</t>
   </si>
@@ -346,9 +347,6 @@
     <t>3月底</t>
   </si>
   <si>
-    <t>️</t>
-  </si>
-  <si>
     <t>✔</t>
   </si>
   <si>
@@ -424,10 +422,6 @@
     <t>阅读训练</t>
   </si>
   <si>
-    <t>软考_高级
-（报名2月底，考试5月下旬）</t>
-  </si>
-  <si>
     <t>B站软考高级视频</t>
   </si>
   <si>
@@ -463,9 +457,6 @@
   </si>
   <si>
     <t>7月底</t>
-  </si>
-  <si>
-    <t>PMP考试（预计9月考试）</t>
   </si>
   <si>
     <t>PMP现代卓越教程</t>
@@ -895,6 +886,27 @@
   </si>
   <si>
     <t>在西西弗斯书店读完了平凡的世界第一本，书中描写的上个世纪在一个贫困的山村中，一家人如何生存。读着读着，仿佛是在看自己家族的兴衰史，家中的大姨总是无论如何也要在时代中拼搏前进，我妈也在这个时代中不断的顽强向前。仿佛是在读自己家中的故事。</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>✔</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>PMP考试（6月考试）</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>软考_高级
+（报名3月，考试5月下旬）</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>《史记的读法》</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>通过这本书通俗的理解了史记中的各种形形色色的人物，有时候觉得人生真是无常，史记当中冷静的春秋笔法让整本书读起来更加冷静</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
@@ -1035,7 +1047,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1111,6 +1123,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC66FF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1248,7 +1272,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="171">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1570,6 +1594,48 @@
     <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="180" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1726,41 +1792,14 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2045,7 +2084,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:J6"/>
+  <dimension ref="B1:J7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" style="90"/>
@@ -2060,15 +2099,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="78" customHeight="1">
-      <c r="B1" s="107" t="s">
-        <v>229</v>
-      </c>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
+      <c r="B1" s="121" t="s">
+        <v>226</v>
+      </c>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
     </row>
     <row r="2" spans="2:10" ht="20" customHeight="1">
       <c r="B2" s="91" t="s">
@@ -2103,7 +2142,7 @@
         <v>7</v>
       </c>
       <c r="D3" s="93" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E3" s="93" t="s">
         <v>9</v>
@@ -2151,10 +2190,10 @@
         <v>7</v>
       </c>
       <c r="D5" s="93" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E5" s="93" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F5" s="93" t="s">
         <v>10</v>
@@ -2163,7 +2202,7 @@
         <v>44591</v>
       </c>
       <c r="H5" s="95" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" spans="2:10" ht="90" customHeight="1">
@@ -2171,22 +2210,45 @@
         <v>4</v>
       </c>
       <c r="C6" s="93" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D6" s="93" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E6" s="93" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F6" s="93" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G6" s="101">
         <v>44619</v>
       </c>
       <c r="H6" s="95" t="s">
-        <v>253</v>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" ht="186" customHeight="1">
+      <c r="B7" s="93">
+        <v>5</v>
+      </c>
+      <c r="C7" s="93" t="s">
+        <v>248</v>
+      </c>
+      <c r="D7" s="93" t="s">
+        <v>223</v>
+      </c>
+      <c r="E7" s="93" t="s">
+        <v>254</v>
+      </c>
+      <c r="F7" s="93" t="s">
+        <v>247</v>
+      </c>
+      <c r="G7" s="101">
+        <v>44636</v>
+      </c>
+      <c r="H7" s="95" t="s">
+        <v>255</v>
       </c>
     </row>
   </sheetData>
@@ -2215,15 +2277,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="90" customFormat="1" ht="78" customHeight="1">
-      <c r="A1" s="109" t="s">
-        <v>223</v>
-      </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="111"/>
-      <c r="G1" s="112"/>
+      <c r="A1" s="123" t="s">
+        <v>220</v>
+      </c>
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="125"/>
+      <c r="G1" s="126"/>
     </row>
     <row r="2" spans="1:7" s="90" customFormat="1" ht="20" customHeight="1">
       <c r="A2" s="91" t="s">
@@ -2282,7 +2344,7 @@
         <v>28</v>
       </c>
       <c r="D4" s="93" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E4" s="93" t="s">
         <v>30</v>
@@ -2322,22 +2384,22 @@
         <v>4</v>
       </c>
       <c r="B6" s="93" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C6" s="93" t="s">
+        <v>221</v>
+      </c>
+      <c r="D6" s="93" t="s">
+        <v>223</v>
+      </c>
+      <c r="E6" s="93" t="s">
         <v>224</v>
-      </c>
-      <c r="D6" s="93" t="s">
-        <v>226</v>
-      </c>
-      <c r="E6" s="93" t="s">
-        <v>227</v>
       </c>
       <c r="F6" s="94">
         <v>44596</v>
       </c>
       <c r="G6" s="95" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="160" customHeight="1">
@@ -2345,22 +2407,22 @@
         <v>5</v>
       </c>
       <c r="B7" s="93" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C7" s="93" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D7" s="93" t="s">
         <v>34</v>
       </c>
       <c r="E7" s="93" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F7" s="94">
         <v>44603</v>
       </c>
       <c r="G7" s="95" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="54" customHeight="1">
@@ -2371,19 +2433,19 @@
         <v>27</v>
       </c>
       <c r="C8" s="93" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D8" s="93" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="93" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F8" s="94">
         <v>44603</v>
       </c>
       <c r="G8" s="95" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="104" customHeight="1">
@@ -2394,19 +2456,19 @@
         <v>27</v>
       </c>
       <c r="C9" s="93" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D9" s="93" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="93" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F9" s="94">
         <v>44610</v>
       </c>
       <c r="G9" s="95" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="78" customHeight="1">
@@ -2417,19 +2479,19 @@
         <v>27</v>
       </c>
       <c r="C10" s="93" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D10" s="93" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E10" s="93" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F10" s="94">
         <v>44611</v>
       </c>
       <c r="G10" s="95" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="20" customHeight="1">
@@ -2440,13 +2502,13 @@
         <v>27</v>
       </c>
       <c r="C11" s="93" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D11" s="93" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E11" s="93" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F11" s="94">
         <v>44619</v>
@@ -2482,44 +2544,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="37" customHeight="1">
-      <c r="B1" s="113" t="s">
+      <c r="B1" s="127" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="114"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="116"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="130"/>
     </row>
     <row r="2" spans="2:10" ht="237" customHeight="1">
-      <c r="B2" s="117" t="s">
+      <c r="B2" s="131" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="118"/>
-      <c r="F2" s="119"/>
-      <c r="G2" s="117"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="131"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="131"/>
     </row>
     <row r="3" spans="2:10" ht="88" customHeight="1">
-      <c r="B3" s="120" t="s">
+      <c r="B3" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="120"/>
-      <c r="D3" s="120"/>
-      <c r="E3" s="121"/>
-      <c r="F3" s="122"/>
-      <c r="G3" s="120"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="134"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="134"/>
     </row>
     <row r="4" spans="2:10" ht="93" customHeight="1">
-      <c r="B4" s="123" t="s">
+      <c r="B4" s="137" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="123"/>
-      <c r="D4" s="123"/>
-      <c r="E4" s="124"/>
-      <c r="F4" s="125"/>
-      <c r="G4" s="126"/>
+      <c r="C4" s="137"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="138"/>
+      <c r="F4" s="139"/>
+      <c r="G4" s="140"/>
     </row>
     <row r="5" spans="2:10" s="27" customFormat="1" ht="50" customHeight="1">
       <c r="B5" s="33" t="s">
@@ -2549,63 +2611,63 @@
       <c r="J5" s="48"/>
     </row>
     <row r="6" spans="2:10" ht="50" customHeight="1">
-      <c r="B6" s="166">
+      <c r="B6" s="114">
         <v>1</v>
       </c>
-      <c r="C6" s="167" t="s">
+      <c r="C6" s="115" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="167" t="s">
+      <c r="D6" s="115" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="168">
+      <c r="E6" s="116">
         <v>44544</v>
       </c>
-      <c r="F6" s="169">
+      <c r="F6" s="117">
         <v>20</v>
       </c>
-      <c r="G6" s="170" t="s">
+      <c r="G6" s="118" t="s">
         <v>50</v>
       </c>
       <c r="H6" s="106"/>
       <c r="I6" s="106"/>
     </row>
     <row r="7" spans="2:10" ht="50" customHeight="1">
-      <c r="B7" s="166">
+      <c r="B7" s="114">
         <v>2</v>
       </c>
-      <c r="C7" s="167" t="s">
+      <c r="C7" s="115" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="167" t="s">
+      <c r="D7" s="115" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="168">
+      <c r="E7" s="116">
         <v>44550</v>
       </c>
-      <c r="F7" s="169">
+      <c r="F7" s="117">
         <v>15</v>
       </c>
-      <c r="G7" s="170" t="s">
+      <c r="G7" s="118" t="s">
         <v>51</v>
       </c>
       <c r="H7" s="106"/>
       <c r="I7" s="106"/>
     </row>
     <row r="8" spans="2:10" ht="50" customHeight="1">
-      <c r="B8" s="166">
+      <c r="B8" s="114">
         <v>3</v>
       </c>
-      <c r="C8" s="167" t="s">
+      <c r="C8" s="115" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="167" t="s">
+      <c r="D8" s="115" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="168">
+      <c r="E8" s="116">
         <v>44560</v>
       </c>
-      <c r="F8" s="169">
+      <c r="F8" s="117">
         <v>25</v>
       </c>
       <c r="G8" s="77" t="s">
@@ -2615,19 +2677,19 @@
       <c r="I8" s="106"/>
     </row>
     <row r="9" spans="2:10" ht="50" customHeight="1">
-      <c r="B9" s="166">
+      <c r="B9" s="114">
         <v>4</v>
       </c>
-      <c r="C9" s="167" t="s">
+      <c r="C9" s="115" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="167" t="s">
+      <c r="D9" s="115" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="168">
+      <c r="E9" s="116">
         <v>44561</v>
       </c>
-      <c r="F9" s="169">
+      <c r="F9" s="117">
         <v>30</v>
       </c>
       <c r="G9" s="77" t="s">
@@ -2637,19 +2699,19 @@
       <c r="I9" s="106"/>
     </row>
     <row r="10" spans="2:10" ht="50" customHeight="1">
-      <c r="B10" s="166">
+      <c r="B10" s="114">
         <v>5</v>
       </c>
-      <c r="C10" s="167" t="s">
+      <c r="C10" s="115" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="167" t="s">
+      <c r="D10" s="115" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="168">
+      <c r="E10" s="116">
         <v>44564</v>
       </c>
-      <c r="F10" s="169" t="s">
+      <c r="F10" s="117" t="s">
         <v>54</v>
       </c>
       <c r="G10" s="77" t="s">
@@ -2659,19 +2721,19 @@
       <c r="I10" s="106"/>
     </row>
     <row r="11" spans="2:10" ht="50" customHeight="1">
-      <c r="B11" s="166">
+      <c r="B11" s="114">
         <v>5</v>
       </c>
-      <c r="C11" s="167" t="s">
+      <c r="C11" s="115" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="167" t="s">
+      <c r="D11" s="115" t="s">
         <v>49</v>
       </c>
-      <c r="E11" s="168">
+      <c r="E11" s="116">
         <v>44569</v>
       </c>
-      <c r="F11" s="169" t="s">
+      <c r="F11" s="117" t="s">
         <v>54</v>
       </c>
       <c r="G11" s="77" t="s">
@@ -2842,8 +2904,8 @@
     </row>
     <row r="28" spans="2:9" s="51" customFormat="1" ht="30" customHeight="1">
       <c r="B28" s="59"/>
-      <c r="C28" s="129"/>
-      <c r="D28" s="129"/>
+      <c r="C28" s="143"/>
+      <c r="D28" s="143"/>
       <c r="E28" s="69"/>
       <c r="F28" s="70"/>
       <c r="G28" s="71"/>
@@ -2852,8 +2914,8 @@
     </row>
     <row r="29" spans="2:9" s="51" customFormat="1" ht="30" customHeight="1">
       <c r="B29" s="59"/>
-      <c r="C29" s="130"/>
-      <c r="D29" s="130"/>
+      <c r="C29" s="144"/>
+      <c r="D29" s="144"/>
       <c r="E29" s="69"/>
       <c r="F29" s="70"/>
       <c r="G29" s="71"/>
@@ -2862,8 +2924,8 @@
     </row>
     <row r="30" spans="2:9" s="51" customFormat="1" ht="30" customHeight="1">
       <c r="B30" s="59"/>
-      <c r="C30" s="130"/>
-      <c r="D30" s="130"/>
+      <c r="C30" s="144"/>
+      <c r="D30" s="144"/>
       <c r="E30" s="69"/>
       <c r="F30" s="70"/>
       <c r="G30" s="71"/>
@@ -2872,8 +2934,8 @@
     </row>
     <row r="31" spans="2:9" s="48" customFormat="1" ht="30" customHeight="1">
       <c r="B31" s="59"/>
-      <c r="C31" s="130"/>
-      <c r="D31" s="130"/>
+      <c r="C31" s="144"/>
+      <c r="D31" s="144"/>
       <c r="E31" s="69"/>
       <c r="F31" s="70"/>
       <c r="G31" s="71"/>
@@ -2882,38 +2944,38 @@
     </row>
     <row r="32" spans="2:9" s="48" customFormat="1" ht="30" customHeight="1">
       <c r="B32" s="59"/>
-      <c r="C32" s="130"/>
-      <c r="D32" s="130"/>
+      <c r="C32" s="144"/>
+      <c r="D32" s="144"/>
       <c r="E32" s="72"/>
       <c r="F32" s="73"/>
       <c r="G32" s="67"/>
-      <c r="H32" s="127"/>
-      <c r="I32" s="127"/>
+      <c r="H32" s="141"/>
+      <c r="I32" s="141"/>
     </row>
     <row r="33" spans="2:10" s="48" customFormat="1" ht="30" customHeight="1">
       <c r="B33" s="59"/>
-      <c r="C33" s="130"/>
-      <c r="D33" s="130"/>
+      <c r="C33" s="144"/>
+      <c r="D33" s="144"/>
       <c r="E33" s="69"/>
       <c r="F33" s="73"/>
       <c r="G33" s="67"/>
-      <c r="H33" s="127"/>
-      <c r="I33" s="127"/>
+      <c r="H33" s="141"/>
+      <c r="I33" s="141"/>
     </row>
     <row r="34" spans="2:10" s="48" customFormat="1" ht="30" customHeight="1">
       <c r="B34" s="59"/>
-      <c r="C34" s="130"/>
-      <c r="D34" s="130"/>
+      <c r="C34" s="144"/>
+      <c r="D34" s="144"/>
       <c r="E34" s="69"/>
       <c r="F34" s="75"/>
       <c r="G34" s="67"/>
-      <c r="H34" s="128"/>
-      <c r="I34" s="128"/>
+      <c r="H34" s="142"/>
+      <c r="I34" s="142"/>
     </row>
     <row r="35" spans="2:10" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B35" s="59"/>
-      <c r="C35" s="130"/>
-      <c r="D35" s="130"/>
+      <c r="C35" s="144"/>
+      <c r="D35" s="144"/>
       <c r="E35" s="69"/>
       <c r="F35" s="75"/>
       <c r="G35" s="77"/>
@@ -2922,8 +2984,8 @@
     </row>
     <row r="36" spans="2:10" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B36" s="59"/>
-      <c r="C36" s="130"/>
-      <c r="D36" s="130"/>
+      <c r="C36" s="144"/>
+      <c r="D36" s="144"/>
       <c r="E36" s="69"/>
       <c r="F36" s="75"/>
       <c r="G36" s="77"/>
@@ -2932,18 +2994,18 @@
     </row>
     <row r="37" spans="2:10" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B37" s="59"/>
-      <c r="C37" s="131"/>
-      <c r="D37" s="131"/>
+      <c r="C37" s="145"/>
+      <c r="D37" s="145"/>
       <c r="E37" s="69"/>
       <c r="F37" s="75"/>
       <c r="G37" s="77"/>
-      <c r="H37" s="127"/>
-      <c r="I37" s="127"/>
+      <c r="H37" s="141"/>
+      <c r="I37" s="141"/>
     </row>
     <row r="38" spans="2:10" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B38" s="60"/>
-      <c r="C38" s="132"/>
-      <c r="D38" s="138"/>
+      <c r="C38" s="146"/>
+      <c r="D38" s="152"/>
       <c r="E38" s="78"/>
       <c r="F38" s="75"/>
       <c r="G38" s="67"/>
@@ -2952,18 +3014,18 @@
     </row>
     <row r="39" spans="2:10" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B39" s="60"/>
-      <c r="C39" s="133"/>
-      <c r="D39" s="139"/>
+      <c r="C39" s="147"/>
+      <c r="D39" s="153"/>
       <c r="E39" s="78"/>
       <c r="F39" s="75"/>
       <c r="G39" s="67"/>
-      <c r="H39" s="128"/>
-      <c r="I39" s="128"/>
+      <c r="H39" s="142"/>
+      <c r="I39" s="142"/>
     </row>
     <row r="40" spans="2:10" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B40" s="60"/>
-      <c r="C40" s="133"/>
-      <c r="D40" s="139"/>
+      <c r="C40" s="147"/>
+      <c r="D40" s="153"/>
       <c r="E40" s="78"/>
       <c r="F40" s="75"/>
       <c r="G40" s="67"/>
@@ -2973,41 +3035,41 @@
     </row>
     <row r="41" spans="2:10" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B41" s="60"/>
-      <c r="C41" s="133"/>
-      <c r="D41" s="139"/>
+      <c r="C41" s="147"/>
+      <c r="D41" s="153"/>
       <c r="E41" s="78"/>
       <c r="F41" s="75"/>
       <c r="G41" s="67"/>
-      <c r="H41" s="128"/>
-      <c r="I41" s="128"/>
+      <c r="H41" s="142"/>
+      <c r="I41" s="142"/>
       <c r="J41" s="84"/>
     </row>
     <row r="42" spans="2:10" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B42" s="60"/>
-      <c r="C42" s="133"/>
-      <c r="D42" s="139"/>
+      <c r="C42" s="147"/>
+      <c r="D42" s="153"/>
       <c r="E42" s="78"/>
       <c r="F42" s="75"/>
       <c r="G42" s="67"/>
-      <c r="H42" s="128"/>
-      <c r="I42" s="128"/>
+      <c r="H42" s="142"/>
+      <c r="I42" s="142"/>
       <c r="J42" s="84"/>
     </row>
     <row r="43" spans="2:10" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B43" s="60"/>
-      <c r="C43" s="133"/>
-      <c r="D43" s="139"/>
+      <c r="C43" s="147"/>
+      <c r="D43" s="153"/>
       <c r="E43" s="78"/>
       <c r="F43" s="75"/>
       <c r="G43" s="67"/>
-      <c r="H43" s="128"/>
-      <c r="I43" s="128"/>
+      <c r="H43" s="142"/>
+      <c r="I43" s="142"/>
       <c r="J43" s="84"/>
     </row>
     <row r="44" spans="2:10" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B44" s="60"/>
-      <c r="C44" s="133"/>
-      <c r="D44" s="139"/>
+      <c r="C44" s="147"/>
+      <c r="D44" s="153"/>
       <c r="E44" s="78"/>
       <c r="F44" s="75"/>
       <c r="G44" s="67"/>
@@ -3017,8 +3079,8 @@
     </row>
     <row r="45" spans="2:10" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B45" s="60"/>
-      <c r="C45" s="133"/>
-      <c r="D45" s="139"/>
+      <c r="C45" s="147"/>
+      <c r="D45" s="153"/>
       <c r="E45" s="78"/>
       <c r="F45" s="75"/>
       <c r="G45" s="67"/>
@@ -3028,8 +3090,8 @@
     </row>
     <row r="46" spans="2:10" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B46" s="60"/>
-      <c r="C46" s="133"/>
-      <c r="D46" s="139"/>
+      <c r="C46" s="147"/>
+      <c r="D46" s="153"/>
       <c r="E46" s="78"/>
       <c r="F46" s="75"/>
       <c r="G46" s="67"/>
@@ -3039,8 +3101,8 @@
     </row>
     <row r="47" spans="2:10" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B47" s="60"/>
-      <c r="C47" s="133"/>
-      <c r="D47" s="139"/>
+      <c r="C47" s="147"/>
+      <c r="D47" s="153"/>
       <c r="E47" s="78"/>
       <c r="F47" s="75"/>
       <c r="G47" s="67"/>
@@ -3050,8 +3112,8 @@
     </row>
     <row r="48" spans="2:10" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B48" s="60"/>
-      <c r="C48" s="133"/>
-      <c r="D48" s="139"/>
+      <c r="C48" s="147"/>
+      <c r="D48" s="153"/>
       <c r="E48" s="78"/>
       <c r="F48" s="75"/>
       <c r="G48" s="67"/>
@@ -3061,8 +3123,8 @@
     </row>
     <row r="49" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B49" s="60"/>
-      <c r="C49" s="133"/>
-      <c r="D49" s="139"/>
+      <c r="C49" s="147"/>
+      <c r="D49" s="153"/>
       <c r="E49" s="78"/>
       <c r="F49" s="75"/>
       <c r="G49" s="67"/>
@@ -3071,8 +3133,8 @@
     </row>
     <row r="50" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B50" s="60"/>
-      <c r="C50" s="133"/>
-      <c r="D50" s="139"/>
+      <c r="C50" s="147"/>
+      <c r="D50" s="153"/>
       <c r="E50" s="78"/>
       <c r="F50" s="75"/>
       <c r="G50" s="67"/>
@@ -3081,8 +3143,8 @@
     </row>
     <row r="51" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B51" s="60"/>
-      <c r="C51" s="133"/>
-      <c r="D51" s="139"/>
+      <c r="C51" s="147"/>
+      <c r="D51" s="153"/>
       <c r="E51" s="78"/>
       <c r="F51" s="75"/>
       <c r="G51" s="79"/>
@@ -3091,8 +3153,8 @@
     </row>
     <row r="52" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B52" s="60"/>
-      <c r="C52" s="133"/>
-      <c r="D52" s="139"/>
+      <c r="C52" s="147"/>
+      <c r="D52" s="153"/>
       <c r="E52" s="78"/>
       <c r="F52" s="75"/>
       <c r="G52" s="79"/>
@@ -3101,8 +3163,8 @@
     </row>
     <row r="53" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B53" s="60"/>
-      <c r="C53" s="133"/>
-      <c r="D53" s="139"/>
+      <c r="C53" s="147"/>
+      <c r="D53" s="153"/>
       <c r="E53" s="78"/>
       <c r="F53" s="75"/>
       <c r="G53" s="79"/>
@@ -3111,8 +3173,8 @@
     </row>
     <row r="54" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B54" s="60"/>
-      <c r="C54" s="133"/>
-      <c r="D54" s="139"/>
+      <c r="C54" s="147"/>
+      <c r="D54" s="153"/>
       <c r="E54" s="78"/>
       <c r="F54" s="75"/>
       <c r="G54" s="81"/>
@@ -3121,8 +3183,8 @@
     </row>
     <row r="55" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B55" s="60"/>
-      <c r="C55" s="133"/>
-      <c r="D55" s="139"/>
+      <c r="C55" s="147"/>
+      <c r="D55" s="153"/>
       <c r="E55" s="78"/>
       <c r="F55" s="75"/>
       <c r="G55" s="82"/>
@@ -3131,8 +3193,8 @@
     </row>
     <row r="56" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B56" s="60"/>
-      <c r="C56" s="133"/>
-      <c r="D56" s="139"/>
+      <c r="C56" s="147"/>
+      <c r="D56" s="153"/>
       <c r="E56" s="78"/>
       <c r="F56" s="75"/>
       <c r="G56" s="82"/>
@@ -3141,8 +3203,8 @@
     </row>
     <row r="57" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B57" s="60"/>
-      <c r="C57" s="133"/>
-      <c r="D57" s="139"/>
+      <c r="C57" s="147"/>
+      <c r="D57" s="153"/>
       <c r="E57" s="78"/>
       <c r="F57" s="75"/>
       <c r="G57" s="82"/>
@@ -3151,8 +3213,8 @@
     </row>
     <row r="58" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B58" s="60"/>
-      <c r="C58" s="133"/>
-      <c r="D58" s="139"/>
+      <c r="C58" s="147"/>
+      <c r="D58" s="153"/>
       <c r="E58" s="78"/>
       <c r="F58" s="75"/>
       <c r="G58" s="82"/>
@@ -3161,8 +3223,8 @@
     </row>
     <row r="59" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B59" s="60"/>
-      <c r="C59" s="133"/>
-      <c r="D59" s="139"/>
+      <c r="C59" s="147"/>
+      <c r="D59" s="153"/>
       <c r="E59" s="78"/>
       <c r="F59" s="75"/>
       <c r="G59" s="82"/>
@@ -3171,8 +3233,8 @@
     </row>
     <row r="60" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B60" s="60"/>
-      <c r="C60" s="133"/>
-      <c r="D60" s="139"/>
+      <c r="C60" s="147"/>
+      <c r="D60" s="153"/>
       <c r="E60" s="78"/>
       <c r="F60" s="75"/>
       <c r="G60" s="67"/>
@@ -3181,8 +3243,8 @@
     </row>
     <row r="61" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B61" s="60"/>
-      <c r="C61" s="133"/>
-      <c r="D61" s="139"/>
+      <c r="C61" s="147"/>
+      <c r="D61" s="153"/>
       <c r="E61" s="78"/>
       <c r="F61" s="75"/>
       <c r="G61" s="67"/>
@@ -3191,8 +3253,8 @@
     </row>
     <row r="62" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B62" s="60"/>
-      <c r="C62" s="133"/>
-      <c r="D62" s="139"/>
+      <c r="C62" s="147"/>
+      <c r="D62" s="153"/>
       <c r="E62" s="78"/>
       <c r="F62" s="75"/>
       <c r="G62" s="67"/>
@@ -3201,8 +3263,8 @@
     </row>
     <row r="63" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B63" s="60"/>
-      <c r="C63" s="133"/>
-      <c r="D63" s="139"/>
+      <c r="C63" s="147"/>
+      <c r="D63" s="153"/>
       <c r="E63" s="78"/>
       <c r="F63" s="75"/>
       <c r="G63" s="67"/>
@@ -3211,8 +3273,8 @@
     </row>
     <row r="64" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B64" s="60"/>
-      <c r="C64" s="133"/>
-      <c r="D64" s="139"/>
+      <c r="C64" s="147"/>
+      <c r="D64" s="153"/>
       <c r="E64" s="78"/>
       <c r="F64" s="75"/>
       <c r="G64" s="67"/>
@@ -3221,8 +3283,8 @@
     </row>
     <row r="65" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B65" s="60"/>
-      <c r="C65" s="133"/>
-      <c r="D65" s="139"/>
+      <c r="C65" s="147"/>
+      <c r="D65" s="153"/>
       <c r="E65" s="78"/>
       <c r="F65" s="75"/>
       <c r="G65" s="67"/>
@@ -3231,8 +3293,8 @@
     </row>
     <row r="66" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B66" s="60"/>
-      <c r="C66" s="133"/>
-      <c r="D66" s="139"/>
+      <c r="C66" s="147"/>
+      <c r="D66" s="153"/>
       <c r="E66" s="78"/>
       <c r="F66" s="75"/>
       <c r="G66" s="67"/>
@@ -3241,8 +3303,8 @@
     </row>
     <row r="67" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B67" s="60"/>
-      <c r="C67" s="134"/>
-      <c r="D67" s="140"/>
+      <c r="C67" s="148"/>
+      <c r="D67" s="154"/>
       <c r="E67" s="78"/>
       <c r="F67" s="85"/>
       <c r="G67" s="67"/>
@@ -3251,8 +3313,8 @@
     </row>
     <row r="68" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B68" s="60"/>
-      <c r="C68" s="135"/>
-      <c r="D68" s="141"/>
+      <c r="C68" s="149"/>
+      <c r="D68" s="155"/>
       <c r="E68" s="78"/>
       <c r="F68" s="86"/>
       <c r="G68" s="77"/>
@@ -3261,8 +3323,8 @@
     </row>
     <row r="69" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B69" s="60"/>
-      <c r="C69" s="136"/>
-      <c r="D69" s="142"/>
+      <c r="C69" s="150"/>
+      <c r="D69" s="156"/>
       <c r="E69" s="78"/>
       <c r="F69" s="86"/>
       <c r="G69" s="77"/>
@@ -3271,8 +3333,8 @@
     </row>
     <row r="70" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B70" s="60"/>
-      <c r="C70" s="136"/>
-      <c r="D70" s="142"/>
+      <c r="C70" s="150"/>
+      <c r="D70" s="156"/>
       <c r="E70" s="78"/>
       <c r="F70" s="86"/>
       <c r="G70" s="77"/>
@@ -3281,8 +3343,8 @@
     </row>
     <row r="71" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B71" s="60"/>
-      <c r="C71" s="136"/>
-      <c r="D71" s="142"/>
+      <c r="C71" s="150"/>
+      <c r="D71" s="156"/>
       <c r="E71" s="78"/>
       <c r="F71" s="86"/>
       <c r="G71" s="77"/>
@@ -3291,8 +3353,8 @@
     </row>
     <row r="72" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B72" s="60"/>
-      <c r="C72" s="136"/>
-      <c r="D72" s="142"/>
+      <c r="C72" s="150"/>
+      <c r="D72" s="156"/>
       <c r="E72" s="78"/>
       <c r="F72" s="87"/>
       <c r="G72" s="77"/>
@@ -3301,8 +3363,8 @@
     </row>
     <row r="73" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B73" s="60"/>
-      <c r="C73" s="136"/>
-      <c r="D73" s="142"/>
+      <c r="C73" s="150"/>
+      <c r="D73" s="156"/>
       <c r="E73" s="78"/>
       <c r="F73" s="87"/>
       <c r="G73" s="77"/>
@@ -3311,8 +3373,8 @@
     </row>
     <row r="74" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B74" s="60"/>
-      <c r="C74" s="136"/>
-      <c r="D74" s="142"/>
+      <c r="C74" s="150"/>
+      <c r="D74" s="156"/>
       <c r="E74" s="78"/>
       <c r="F74" s="87"/>
       <c r="G74" s="77"/>
@@ -3321,8 +3383,8 @@
     </row>
     <row r="75" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B75" s="60"/>
-      <c r="C75" s="136"/>
-      <c r="D75" s="142"/>
+      <c r="C75" s="150"/>
+      <c r="D75" s="156"/>
       <c r="E75" s="78"/>
       <c r="F75" s="75"/>
       <c r="G75" s="77"/>
@@ -3331,8 +3393,8 @@
     </row>
     <row r="76" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B76" s="60"/>
-      <c r="C76" s="136"/>
-      <c r="D76" s="142"/>
+      <c r="C76" s="150"/>
+      <c r="D76" s="156"/>
       <c r="E76" s="78"/>
       <c r="F76" s="85"/>
       <c r="G76" s="77"/>
@@ -3341,8 +3403,8 @@
     </row>
     <row r="77" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B77" s="60"/>
-      <c r="C77" s="136"/>
-      <c r="D77" s="142"/>
+      <c r="C77" s="150"/>
+      <c r="D77" s="156"/>
       <c r="E77" s="78"/>
       <c r="F77" s="86"/>
       <c r="G77" s="77"/>
@@ -3351,8 +3413,8 @@
     </row>
     <row r="78" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B78" s="60"/>
-      <c r="C78" s="136"/>
-      <c r="D78" s="142"/>
+      <c r="C78" s="150"/>
+      <c r="D78" s="156"/>
       <c r="E78" s="78"/>
       <c r="F78" s="86"/>
       <c r="G78" s="77"/>
@@ -3361,8 +3423,8 @@
     </row>
     <row r="79" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B79" s="60"/>
-      <c r="C79" s="136"/>
-      <c r="D79" s="142"/>
+      <c r="C79" s="150"/>
+      <c r="D79" s="156"/>
       <c r="E79" s="78"/>
       <c r="F79" s="86"/>
       <c r="G79" s="77"/>
@@ -3371,8 +3433,8 @@
     </row>
     <row r="80" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B80" s="60"/>
-      <c r="C80" s="136"/>
-      <c r="D80" s="142"/>
+      <c r="C80" s="150"/>
+      <c r="D80" s="156"/>
       <c r="E80" s="78"/>
       <c r="F80" s="86"/>
       <c r="G80" s="77"/>
@@ -3381,8 +3443,8 @@
     </row>
     <row r="81" spans="2:9" s="52" customFormat="1" ht="30" customHeight="1">
       <c r="B81" s="60"/>
-      <c r="C81" s="136"/>
-      <c r="D81" s="142"/>
+      <c r="C81" s="150"/>
+      <c r="D81" s="156"/>
       <c r="E81" s="78"/>
       <c r="F81" s="87"/>
       <c r="G81" s="77"/>
@@ -3391,8 +3453,8 @@
     </row>
     <row r="82" spans="2:9" ht="30" customHeight="1">
       <c r="B82" s="60"/>
-      <c r="C82" s="136"/>
-      <c r="D82" s="142"/>
+      <c r="C82" s="150"/>
+      <c r="D82" s="156"/>
       <c r="E82" s="78"/>
       <c r="F82" s="87"/>
       <c r="G82" s="77"/>
@@ -3401,8 +3463,8 @@
     </row>
     <row r="83" spans="2:9" ht="30" customHeight="1">
       <c r="B83" s="60"/>
-      <c r="C83" s="136"/>
-      <c r="D83" s="142"/>
+      <c r="C83" s="150"/>
+      <c r="D83" s="156"/>
       <c r="E83" s="78"/>
       <c r="F83" s="87"/>
       <c r="G83" s="77"/>
@@ -3411,8 +3473,8 @@
     </row>
     <row r="84" spans="2:9" ht="30" customHeight="1">
       <c r="B84" s="60"/>
-      <c r="C84" s="136"/>
-      <c r="D84" s="142"/>
+      <c r="C84" s="150"/>
+      <c r="D84" s="156"/>
       <c r="E84" s="78"/>
       <c r="F84" s="87"/>
       <c r="G84" s="77"/>
@@ -3421,8 +3483,8 @@
     </row>
     <row r="85" spans="2:9" ht="30" customHeight="1">
       <c r="B85" s="60"/>
-      <c r="C85" s="136"/>
-      <c r="D85" s="142"/>
+      <c r="C85" s="150"/>
+      <c r="D85" s="156"/>
       <c r="E85" s="78"/>
       <c r="F85" s="87"/>
       <c r="G85" s="77"/>
@@ -3431,8 +3493,8 @@
     </row>
     <row r="86" spans="2:9" ht="30" customHeight="1">
       <c r="B86" s="60"/>
-      <c r="C86" s="136"/>
-      <c r="D86" s="142"/>
+      <c r="C86" s="150"/>
+      <c r="D86" s="156"/>
       <c r="E86" s="78"/>
       <c r="F86" s="87"/>
       <c r="G86" s="77"/>
@@ -3441,8 +3503,8 @@
     </row>
     <row r="87" spans="2:9" ht="30" customHeight="1">
       <c r="B87" s="60"/>
-      <c r="C87" s="137"/>
-      <c r="D87" s="143"/>
+      <c r="C87" s="151"/>
+      <c r="D87" s="157"/>
       <c r="E87" s="78"/>
       <c r="F87" s="87"/>
       <c r="G87" s="77"/>
@@ -3497,56 +3559,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="110" customHeight="1">
-      <c r="B1" s="113" t="s">
+      <c r="B1" s="127" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="145"/>
-      <c r="J1" s="146"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="158"/>
+      <c r="F1" s="158"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="160"/>
     </row>
     <row r="2" spans="2:13" ht="190" customHeight="1">
-      <c r="B2" s="117" t="s">
+      <c r="B2" s="131" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="148"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="148"/>
-      <c r="J2" s="117"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="131"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="162"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="162"/>
+      <c r="J2" s="131"/>
     </row>
     <row r="3" spans="2:13" ht="94" customHeight="1">
-      <c r="B3" s="120" t="s">
+      <c r="B3" s="134" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="120"/>
-      <c r="D3" s="120"/>
-      <c r="E3" s="149"/>
-      <c r="F3" s="149"/>
-      <c r="G3" s="150"/>
-      <c r="H3" s="149"/>
-      <c r="I3" s="150"/>
-      <c r="J3" s="120"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="134"/>
+      <c r="E3" s="163"/>
+      <c r="F3" s="163"/>
+      <c r="G3" s="164"/>
+      <c r="H3" s="163"/>
+      <c r="I3" s="164"/>
+      <c r="J3" s="134"/>
     </row>
     <row r="4" spans="2:13" ht="67" customHeight="1">
-      <c r="B4" s="120" t="s">
+      <c r="B4" s="134" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="120"/>
-      <c r="D4" s="120"/>
-      <c r="E4" s="149"/>
-      <c r="F4" s="149"/>
-      <c r="G4" s="150"/>
-      <c r="H4" s="149"/>
-      <c r="I4" s="150"/>
-      <c r="J4" s="120"/>
+      <c r="C4" s="134"/>
+      <c r="D4" s="134"/>
+      <c r="E4" s="163"/>
+      <c r="F4" s="163"/>
+      <c r="G4" s="164"/>
+      <c r="H4" s="163"/>
+      <c r="I4" s="164"/>
+      <c r="J4" s="134"/>
     </row>
     <row r="5" spans="2:13" s="27" customFormat="1" ht="50" customHeight="1">
       <c r="B5" s="33" t="s">
@@ -3581,87 +3643,87 @@
       <c r="M5" s="48"/>
     </row>
     <row r="6" spans="2:13" ht="50" customHeight="1">
-      <c r="B6" s="159">
+      <c r="B6" s="107">
         <v>1</v>
       </c>
-      <c r="C6" s="160" t="s">
+      <c r="C6" s="108" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="161" t="s">
+      <c r="D6" s="109" t="s">
         <v>66</v>
       </c>
-      <c r="E6" s="162">
+      <c r="E6" s="110">
         <v>44543</v>
       </c>
-      <c r="F6" s="163">
+      <c r="F6" s="111">
         <v>44548</v>
       </c>
-      <c r="G6" s="164">
+      <c r="G6" s="112">
         <f t="shared" ref="G6:G8" si="0">F6-E6</f>
         <v>5</v>
       </c>
-      <c r="H6" s="163">
+      <c r="H6" s="111">
         <v>44562</v>
       </c>
-      <c r="I6" s="164">
+      <c r="I6" s="112">
         <f>H6-E6</f>
         <v>19</v>
       </c>
-      <c r="J6" s="165" t="s">
+      <c r="J6" s="113" t="s">
         <v>67</v>
       </c>
       <c r="K6" s="52"/>
       <c r="L6" s="52"/>
     </row>
     <row r="7" spans="2:13" ht="50" customHeight="1">
-      <c r="B7" s="159">
+      <c r="B7" s="107">
         <v>2</v>
       </c>
-      <c r="C7" s="160" t="s">
+      <c r="C7" s="108" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="161" t="s">
+      <c r="D7" s="109" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="162">
+      <c r="E7" s="110">
         <v>44549</v>
       </c>
-      <c r="F7" s="163">
+      <c r="F7" s="111">
         <v>44559</v>
       </c>
-      <c r="G7" s="164">
+      <c r="G7" s="112">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="H7" s="163"/>
-      <c r="I7" s="164"/>
-      <c r="J7" s="165"/>
+      <c r="H7" s="111"/>
+      <c r="I7" s="112"/>
+      <c r="J7" s="113"/>
       <c r="K7" s="52"/>
       <c r="L7" s="52"/>
     </row>
     <row r="8" spans="2:13" ht="50" customHeight="1">
-      <c r="B8" s="159">
+      <c r="B8" s="107">
         <v>3</v>
       </c>
-      <c r="C8" s="160" t="s">
+      <c r="C8" s="108" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="161" t="s">
+      <c r="D8" s="109" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="162">
+      <c r="E8" s="110">
         <v>44560</v>
       </c>
-      <c r="F8" s="163">
+      <c r="F8" s="111">
         <v>44565</v>
       </c>
-      <c r="G8" s="164">
+      <c r="G8" s="112">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="H8" s="163"/>
-      <c r="I8" s="164"/>
-      <c r="J8" s="165"/>
+      <c r="H8" s="111"/>
+      <c r="I8" s="112"/>
+      <c r="J8" s="113"/>
       <c r="K8" s="52"/>
       <c r="L8" s="52"/>
     </row>
@@ -3875,16 +3937,16 @@
       </c>
     </row>
     <row r="2" spans="1:20" ht="20" customHeight="1">
-      <c r="A2" s="151">
+      <c r="A2" s="165">
         <v>1</v>
       </c>
-      <c r="B2" s="151" t="s">
+      <c r="B2" s="165" t="s">
         <v>88</v>
       </c>
-      <c r="C2" s="151" t="s">
+      <c r="C2" s="165" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="151" t="s">
+      <c r="D2" s="165" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="6" t="s">
@@ -3899,9 +3961,7 @@
       </c>
       <c r="H2" s="7"/>
       <c r="I2" s="20"/>
-      <c r="J2" s="20" t="s">
-        <v>92</v>
-      </c>
+      <c r="J2" s="20"/>
       <c r="K2" s="7"/>
       <c r="L2" s="7"/>
       <c r="M2" s="7"/>
@@ -3912,19 +3972,19 @@
       <c r="R2" s="7"/>
       <c r="S2" s="7"/>
       <c r="T2" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="20" customHeight="1">
+      <c r="A3" s="165"/>
+      <c r="B3" s="165"/>
+      <c r="C3" s="165"/>
+      <c r="D3" s="165"/>
+      <c r="E3" s="6" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" ht="20" customHeight="1">
-      <c r="A3" s="151"/>
-      <c r="B3" s="151"/>
-      <c r="C3" s="151"/>
-      <c r="D3" s="151"/>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="7" t="s">
         <v>94</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>95</v>
       </c>
       <c r="G3" s="18">
         <f>COUNTIF(H3:S3,$T$2)/12</f>
@@ -3944,15 +4004,15 @@
       <c r="S3" s="7"/>
     </row>
     <row r="4" spans="1:20" ht="20" customHeight="1">
-      <c r="A4" s="151"/>
-      <c r="B4" s="151"/>
-      <c r="C4" s="151"/>
-      <c r="D4" s="151"/>
+      <c r="A4" s="165"/>
+      <c r="B4" s="165"/>
+      <c r="C4" s="165"/>
+      <c r="D4" s="165"/>
       <c r="E4" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G4" s="18">
         <f>COUNTIF(H4:S4,$T$2)/12</f>
@@ -3972,15 +4032,15 @@
       <c r="S4" s="7"/>
     </row>
     <row r="5" spans="1:20" ht="20" customHeight="1">
-      <c r="A5" s="151"/>
-      <c r="B5" s="151"/>
-      <c r="C5" s="151"/>
-      <c r="D5" s="151"/>
+      <c r="A5" s="165"/>
+      <c r="B5" s="165"/>
+      <c r="C5" s="165"/>
+      <c r="D5" s="165"/>
       <c r="E5" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>97</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>98</v>
       </c>
       <c r="G5" s="18">
         <f t="shared" ref="G5:G24" si="0">COUNTIF(H5:S5,$T$2)/12</f>
@@ -4000,15 +4060,15 @@
       <c r="S5" s="20"/>
     </row>
     <row r="6" spans="1:20" ht="20" customHeight="1">
-      <c r="A6" s="151"/>
-      <c r="B6" s="151"/>
-      <c r="C6" s="151"/>
-      <c r="D6" s="151"/>
+      <c r="A6" s="165"/>
+      <c r="B6" s="165"/>
+      <c r="C6" s="165"/>
+      <c r="D6" s="165"/>
       <c r="E6" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="G6" s="18">
         <f t="shared" si="0"/>
@@ -4028,18 +4088,18 @@
       <c r="S6" s="7"/>
     </row>
     <row r="7" spans="1:20" ht="20" customHeight="1">
-      <c r="A7" s="151">
+      <c r="A7" s="165">
         <v>2</v>
       </c>
-      <c r="B7" s="151"/>
-      <c r="C7" s="151" t="s">
+      <c r="B7" s="165"/>
+      <c r="C7" s="165" t="s">
+        <v>100</v>
+      </c>
+      <c r="D7" s="165" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="D7" s="151" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>102</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>91</v>
@@ -4051,8 +4111,8 @@
       <c r="H7" s="19"/>
       <c r="I7" s="19"/>
       <c r="J7" s="19"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
+      <c r="K7" s="173"/>
+      <c r="L7" s="173"/>
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
@@ -4062,15 +4122,15 @@
       <c r="S7" s="7"/>
     </row>
     <row r="8" spans="1:20" ht="20" customHeight="1">
-      <c r="A8" s="151"/>
-      <c r="B8" s="151"/>
-      <c r="C8" s="151"/>
-      <c r="D8" s="151"/>
+      <c r="A8" s="165"/>
+      <c r="B8" s="165"/>
+      <c r="C8" s="165"/>
+      <c r="D8" s="165"/>
       <c r="E8" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>103</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>104</v>
       </c>
       <c r="G8" s="18">
         <f t="shared" si="0"/>
@@ -4078,8 +4138,8 @@
       </c>
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
+      <c r="J8" s="173"/>
+      <c r="K8" s="173"/>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
@@ -4090,12 +4150,12 @@
       <c r="S8" s="7"/>
     </row>
     <row r="9" spans="1:20" ht="19" customHeight="1">
-      <c r="A9" s="151"/>
-      <c r="B9" s="151"/>
-      <c r="C9" s="151"/>
-      <c r="D9" s="151"/>
+      <c r="A9" s="165"/>
+      <c r="B9" s="165"/>
+      <c r="C9" s="165"/>
+      <c r="D9" s="165"/>
       <c r="E9" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>91</v>
@@ -4107,8 +4167,8 @@
       <c r="H9" s="19"/>
       <c r="I9" s="19"/>
       <c r="J9" s="19"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
+      <c r="K9" s="173"/>
+      <c r="L9" s="173"/>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
@@ -4118,21 +4178,21 @@
       <c r="S9" s="7"/>
     </row>
     <row r="10" spans="1:20" ht="20" customHeight="1">
-      <c r="A10" s="151">
+      <c r="A10" s="165">
         <v>3</v>
       </c>
-      <c r="B10" s="151"/>
-      <c r="C10" s="151" t="s">
+      <c r="B10" s="165"/>
+      <c r="C10" s="165" t="s">
+        <v>105</v>
+      </c>
+      <c r="D10" s="165" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="D10" s="151" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="F10" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G10" s="18">
         <f t="shared" si="0"/>
@@ -4152,12 +4212,12 @@
       <c r="S10" s="7"/>
     </row>
     <row r="11" spans="1:20" ht="20" customHeight="1">
-      <c r="A11" s="151"/>
-      <c r="B11" s="151"/>
-      <c r="C11" s="151"/>
-      <c r="D11" s="151"/>
+      <c r="A11" s="165"/>
+      <c r="B11" s="165"/>
+      <c r="C11" s="165"/>
+      <c r="D11" s="165"/>
       <c r="E11" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>91</v>
@@ -4169,8 +4229,8 @@
       <c r="H11" s="7"/>
       <c r="I11" s="21"/>
       <c r="J11" s="21"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
+      <c r="K11" s="174"/>
+      <c r="L11" s="174"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
@@ -4180,12 +4240,12 @@
       <c r="S11" s="7"/>
     </row>
     <row r="12" spans="1:20" ht="20" customHeight="1">
-      <c r="A12" s="151"/>
-      <c r="B12" s="151"/>
-      <c r="C12" s="151"/>
-      <c r="D12" s="151"/>
+      <c r="A12" s="165"/>
+      <c r="B12" s="165"/>
+      <c r="C12" s="165"/>
+      <c r="D12" s="165"/>
       <c r="E12" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>91</v>
@@ -4197,8 +4257,8 @@
       <c r="H12" s="7"/>
       <c r="I12" s="21"/>
       <c r="J12" s="21"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
+      <c r="K12" s="174"/>
+      <c r="L12" s="174"/>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
       <c r="O12" s="7"/>
@@ -4208,21 +4268,21 @@
       <c r="S12" s="7"/>
     </row>
     <row r="13" spans="1:20" ht="20" customHeight="1">
-      <c r="A13" s="151">
+      <c r="A13" s="165">
         <v>4</v>
       </c>
-      <c r="B13" s="151"/>
-      <c r="C13" s="151" t="s">
+      <c r="B13" s="165"/>
+      <c r="C13" s="165" t="s">
+        <v>109</v>
+      </c>
+      <c r="D13" s="165" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="D13" s="151" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="6" t="s">
+      <c r="F13" s="7" t="s">
         <v>111</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>112</v>
       </c>
       <c r="G13" s="18">
         <f t="shared" si="0"/>
@@ -4242,15 +4302,15 @@
       <c r="S13" s="7"/>
     </row>
     <row r="14" spans="1:20" ht="20" customHeight="1">
-      <c r="A14" s="151"/>
-      <c r="B14" s="151"/>
-      <c r="C14" s="151"/>
-      <c r="D14" s="151"/>
+      <c r="A14" s="165"/>
+      <c r="B14" s="165"/>
+      <c r="C14" s="165"/>
+      <c r="D14" s="165"/>
       <c r="E14" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F14" s="7" t="s">
         <v>113</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>114</v>
       </c>
       <c r="G14" s="18">
         <f t="shared" si="0"/>
@@ -4270,15 +4330,15 @@
       <c r="S14" s="7"/>
     </row>
     <row r="15" spans="1:20" ht="20" customHeight="1">
-      <c r="A15" s="151"/>
-      <c r="B15" s="151"/>
-      <c r="C15" s="151"/>
-      <c r="D15" s="151"/>
+      <c r="A15" s="165"/>
+      <c r="B15" s="165"/>
+      <c r="C15" s="165"/>
+      <c r="D15" s="165"/>
       <c r="E15" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G15" s="18">
         <f t="shared" si="0"/>
@@ -4298,15 +4358,15 @@
       <c r="S15" s="7"/>
     </row>
     <row r="16" spans="1:20" ht="20" customHeight="1">
-      <c r="A16" s="151"/>
-      <c r="B16" s="151"/>
-      <c r="C16" s="151"/>
-      <c r="D16" s="151"/>
+      <c r="A16" s="165"/>
+      <c r="B16" s="165"/>
+      <c r="C16" s="165"/>
+      <c r="D16" s="165"/>
       <c r="E16" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G16" s="18">
         <f t="shared" si="0"/>
@@ -4326,18 +4386,18 @@
       <c r="S16" s="7"/>
     </row>
     <row r="17" spans="1:19" ht="20" customHeight="1">
-      <c r="A17" s="151">
+      <c r="A17" s="165">
         <v>5</v>
       </c>
-      <c r="B17" s="151"/>
-      <c r="C17" s="151" t="s">
-        <v>117</v>
-      </c>
-      <c r="D17" s="151" t="s">
+      <c r="B17" s="165"/>
+      <c r="C17" s="165" t="s">
+        <v>253</v>
+      </c>
+      <c r="D17" s="165" t="s">
         <v>29</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>91</v>
@@ -4360,15 +4420,15 @@
       <c r="S17" s="7"/>
     </row>
     <row r="18" spans="1:19" ht="20" customHeight="1">
-      <c r="A18" s="151"/>
-      <c r="B18" s="151"/>
-      <c r="C18" s="151"/>
-      <c r="D18" s="151"/>
+      <c r="A18" s="165"/>
+      <c r="B18" s="165"/>
+      <c r="C18" s="165"/>
+      <c r="D18" s="165"/>
       <c r="E18" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G18" s="18">
         <f t="shared" si="0"/>
@@ -4388,15 +4448,15 @@
       <c r="S18" s="7"/>
     </row>
     <row r="19" spans="1:19" ht="20" customHeight="1">
-      <c r="A19" s="151"/>
-      <c r="B19" s="151"/>
-      <c r="C19" s="151"/>
-      <c r="D19" s="151"/>
+      <c r="A19" s="165"/>
+      <c r="B19" s="165"/>
+      <c r="C19" s="165"/>
+      <c r="D19" s="165"/>
       <c r="E19" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G19" s="18">
         <f t="shared" si="0"/>
@@ -4416,15 +4476,15 @@
       <c r="S19" s="7"/>
     </row>
     <row r="20" spans="1:19" ht="20" customHeight="1">
-      <c r="A20" s="151"/>
-      <c r="B20" s="151"/>
-      <c r="C20" s="151"/>
-      <c r="D20" s="151"/>
+      <c r="A20" s="165"/>
+      <c r="B20" s="165"/>
+      <c r="C20" s="165"/>
+      <c r="D20" s="165"/>
       <c r="E20" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G20" s="18">
         <f t="shared" si="0"/>
@@ -4444,28 +4504,28 @@
       <c r="S20" s="7"/>
     </row>
     <row r="21" spans="1:19" ht="20" customHeight="1">
-      <c r="A21" s="151">
+      <c r="A21" s="165">
         <v>6</v>
       </c>
-      <c r="B21" s="151"/>
-      <c r="C21" s="151" t="s">
+      <c r="B21" s="165"/>
+      <c r="C21" s="165" t="s">
+        <v>121</v>
+      </c>
+      <c r="D21" s="165" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F21" s="7" t="s">
         <v>123</v>
-      </c>
-      <c r="D21" s="151" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>125</v>
       </c>
       <c r="G21" s="18">
         <f t="shared" si="0"/>
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="7"/>
@@ -4480,22 +4540,22 @@
       <c r="S21" s="7"/>
     </row>
     <row r="22" spans="1:19" ht="20" customHeight="1">
-      <c r="A22" s="151"/>
-      <c r="B22" s="151"/>
-      <c r="C22" s="151"/>
-      <c r="D22" s="151"/>
+      <c r="A22" s="165"/>
+      <c r="B22" s="165"/>
+      <c r="C22" s="165"/>
+      <c r="D22" s="165"/>
       <c r="E22" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G22" s="18">
         <f t="shared" si="0"/>
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
@@ -4510,15 +4570,15 @@
       <c r="S22" s="7"/>
     </row>
     <row r="23" spans="1:19" ht="20" customHeight="1">
-      <c r="A23" s="151"/>
-      <c r="B23" s="151"/>
-      <c r="C23" s="151"/>
-      <c r="D23" s="151"/>
+      <c r="A23" s="165"/>
+      <c r="B23" s="165"/>
+      <c r="C23" s="165"/>
+      <c r="D23" s="165"/>
       <c r="E23" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G23" s="18">
         <f t="shared" si="0"/>
@@ -4538,15 +4598,15 @@
       <c r="S23" s="7"/>
     </row>
     <row r="24" spans="1:19" ht="20" customHeight="1">
-      <c r="A24" s="151"/>
-      <c r="B24" s="151"/>
-      <c r="C24" s="151"/>
-      <c r="D24" s="151"/>
+      <c r="A24" s="165"/>
+      <c r="B24" s="165"/>
+      <c r="C24" s="165"/>
+      <c r="D24" s="165"/>
       <c r="E24" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G24" s="18">
         <f t="shared" si="0"/>
@@ -4566,21 +4626,21 @@
       <c r="S24" s="7"/>
     </row>
     <row r="25" spans="1:19" ht="20" customHeight="1">
-      <c r="A25" s="151">
+      <c r="A25" s="165">
         <v>7</v>
       </c>
-      <c r="B25" s="151"/>
-      <c r="C25" s="151" t="s">
-        <v>130</v>
-      </c>
-      <c r="D25" s="151" t="s">
+      <c r="B25" s="165"/>
+      <c r="C25" s="165" t="s">
+        <v>252</v>
+      </c>
+      <c r="D25" s="165" t="s">
         <v>29</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G25" s="18">
         <f>COUNTIF(H25:S25,$T$2)/12</f>
@@ -4600,15 +4660,15 @@
       <c r="S25" s="7"/>
     </row>
     <row r="26" spans="1:19" ht="20" customHeight="1">
-      <c r="A26" s="151"/>
-      <c r="B26" s="151"/>
-      <c r="C26" s="151"/>
-      <c r="D26" s="151"/>
+      <c r="A26" s="165"/>
+      <c r="B26" s="165"/>
+      <c r="C26" s="165"/>
+      <c r="D26" s="165"/>
       <c r="E26" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G26" s="18">
         <f>COUNTIF(H26:S26,$T$2)/12</f>
@@ -4628,15 +4688,15 @@
       <c r="S26" s="7"/>
     </row>
     <row r="27" spans="1:19" ht="20" customHeight="1">
-      <c r="A27" s="151"/>
-      <c r="B27" s="151"/>
-      <c r="C27" s="151"/>
-      <c r="D27" s="151"/>
+      <c r="A27" s="165"/>
+      <c r="B27" s="165"/>
+      <c r="C27" s="165"/>
+      <c r="D27" s="165"/>
       <c r="E27" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G27" s="18">
         <f t="shared" ref="G27:G36" si="1">COUNTIF(H27:S27,$T$2)/12</f>
@@ -4656,22 +4716,22 @@
       <c r="S27" s="7"/>
     </row>
     <row r="28" spans="1:19" ht="20" customHeight="1">
-      <c r="A28" s="151"/>
-      <c r="B28" s="151"/>
-      <c r="C28" s="151"/>
-      <c r="D28" s="151"/>
+      <c r="A28" s="165"/>
+      <c r="B28" s="165"/>
+      <c r="C28" s="165"/>
+      <c r="D28" s="165"/>
       <c r="E28" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G28" s="18">
         <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="H28" s="19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I28" s="7"/>
       <c r="J28" s="7"/>
@@ -4686,28 +4746,28 @@
       <c r="S28" s="7"/>
     </row>
     <row r="29" spans="1:19" ht="21" customHeight="1">
-      <c r="A29" s="152">
+      <c r="A29" s="166">
         <v>8</v>
       </c>
-      <c r="B29" s="151"/>
-      <c r="C29" s="152" t="s">
-        <v>137</v>
-      </c>
-      <c r="D29" s="152" t="s">
+      <c r="B29" s="165"/>
+      <c r="C29" s="166" t="s">
+        <v>134</v>
+      </c>
+      <c r="D29" s="166" t="s">
         <v>8</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G29" s="18">
         <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="H29" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I29" s="7"/>
       <c r="J29" s="7"/>
@@ -4720,16 +4780,16 @@
       <c r="R29" s="7"/>
       <c r="S29" s="7"/>
     </row>
-    <row r="30" spans="1:19" ht="44" customHeight="1">
-      <c r="A30" s="153"/>
-      <c r="B30" s="151"/>
-      <c r="C30" s="153"/>
-      <c r="D30" s="153"/>
+    <row r="30" spans="1:19" ht="67" customHeight="1">
+      <c r="A30" s="167"/>
+      <c r="B30" s="165"/>
+      <c r="C30" s="167"/>
+      <c r="D30" s="167"/>
       <c r="E30" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G30" s="18">
         <f t="shared" si="1"/>
@@ -4749,21 +4809,21 @@
       <c r="S30" s="7"/>
     </row>
     <row r="31" spans="1:19" ht="20" customHeight="1">
-      <c r="A31" s="152">
+      <c r="A31" s="166">
         <v>9</v>
       </c>
-      <c r="B31" s="151"/>
-      <c r="C31" s="152" t="s">
-        <v>142</v>
+      <c r="B31" s="165"/>
+      <c r="C31" s="166" t="s">
+        <v>139</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>29</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G31" s="18">
         <f t="shared" si="1"/>
@@ -4783,14 +4843,14 @@
       <c r="S31" s="7"/>
     </row>
     <row r="32" spans="1:19" ht="20" customHeight="1">
-      <c r="A32" s="153"/>
-      <c r="B32" s="151"/>
-      <c r="C32" s="153"/>
+      <c r="A32" s="167"/>
+      <c r="B32" s="165"/>
+      <c r="C32" s="167"/>
       <c r="D32" s="7" t="s">
         <v>29</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>91</v>
@@ -4813,23 +4873,23 @@
       <c r="S32" s="7"/>
     </row>
     <row r="33" spans="1:19" ht="20" customHeight="1">
-      <c r="A33" s="152">
+      <c r="A33" s="166">
         <v>1</v>
       </c>
-      <c r="B33" s="152" t="s">
-        <v>145</v>
-      </c>
-      <c r="C33" s="152" t="s">
-        <v>146</v>
-      </c>
-      <c r="D33" s="151" t="s">
+      <c r="B33" s="166" t="s">
+        <v>142</v>
+      </c>
+      <c r="C33" s="166" t="s">
+        <v>143</v>
+      </c>
+      <c r="D33" s="165" t="s">
         <v>29</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G33" s="18">
         <f t="shared" si="1"/>
@@ -4837,7 +4897,7 @@
       </c>
       <c r="H33" s="23"/>
       <c r="I33" s="7"/>
-      <c r="J33" s="7"/>
+      <c r="J33" s="175"/>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
@@ -4849,15 +4909,15 @@
       <c r="S33" s="7"/>
     </row>
     <row r="34" spans="1:19" ht="20" customHeight="1">
-      <c r="A34" s="154"/>
-      <c r="B34" s="154"/>
-      <c r="C34" s="154"/>
-      <c r="D34" s="151"/>
+      <c r="A34" s="168"/>
+      <c r="B34" s="168"/>
+      <c r="C34" s="168"/>
+      <c r="D34" s="165"/>
       <c r="E34" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G34" s="18">
         <f t="shared" si="1"/>
@@ -4877,15 +4937,15 @@
       <c r="S34" s="7"/>
     </row>
     <row r="35" spans="1:19" ht="20" customHeight="1">
-      <c r="A35" s="154"/>
-      <c r="B35" s="154"/>
-      <c r="C35" s="154"/>
-      <c r="D35" s="151"/>
+      <c r="A35" s="168"/>
+      <c r="B35" s="168"/>
+      <c r="C35" s="168"/>
+      <c r="D35" s="165"/>
       <c r="E35" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G35" s="18">
         <f t="shared" si="1"/>
@@ -4905,15 +4965,15 @@
       <c r="S35" s="7"/>
     </row>
     <row r="36" spans="1:19" ht="20" customHeight="1">
-      <c r="A36" s="153"/>
-      <c r="B36" s="154"/>
-      <c r="C36" s="153"/>
-      <c r="D36" s="151"/>
+      <c r="A36" s="167"/>
+      <c r="B36" s="168"/>
+      <c r="C36" s="167"/>
+      <c r="D36" s="165"/>
       <c r="E36" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G36" s="18">
         <f t="shared" si="1"/>
@@ -4933,21 +4993,21 @@
       <c r="S36" s="23"/>
     </row>
     <row r="37" spans="1:19" ht="20" customHeight="1">
-      <c r="A37" s="152">
+      <c r="A37" s="166">
         <v>2</v>
       </c>
-      <c r="B37" s="154"/>
-      <c r="C37" s="152" t="s">
-        <v>151</v>
-      </c>
-      <c r="D37" s="152" t="s">
+      <c r="B37" s="168"/>
+      <c r="C37" s="166" t="s">
+        <v>148</v>
+      </c>
+      <c r="D37" s="166" t="s">
         <v>8</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G37" s="18">
         <f t="shared" ref="G37:G43" si="2">COUNTIF(H37:S37,$T$2)/12</f>
@@ -4967,15 +5027,15 @@
       <c r="S37" s="7"/>
     </row>
     <row r="38" spans="1:19" ht="20" customHeight="1">
-      <c r="A38" s="154"/>
-      <c r="B38" s="154"/>
-      <c r="C38" s="154"/>
-      <c r="D38" s="154"/>
+      <c r="A38" s="168"/>
+      <c r="B38" s="168"/>
+      <c r="C38" s="168"/>
+      <c r="D38" s="168"/>
       <c r="E38" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G38" s="18">
         <f t="shared" si="2"/>
@@ -4995,15 +5055,15 @@
       <c r="S38" s="20"/>
     </row>
     <row r="39" spans="1:19" ht="20" customHeight="1">
-      <c r="A39" s="153"/>
-      <c r="B39" s="154"/>
-      <c r="C39" s="153"/>
-      <c r="D39" s="153"/>
+      <c r="A39" s="167"/>
+      <c r="B39" s="168"/>
+      <c r="C39" s="167"/>
+      <c r="D39" s="167"/>
       <c r="E39" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G39" s="18">
         <f t="shared" si="2"/>
@@ -5023,21 +5083,21 @@
       <c r="S39" s="20"/>
     </row>
     <row r="40" spans="1:19" ht="20" customHeight="1">
-      <c r="A40" s="152">
+      <c r="A40" s="166">
         <v>3</v>
       </c>
-      <c r="B40" s="154"/>
-      <c r="C40" s="152" t="s">
-        <v>155</v>
-      </c>
-      <c r="D40" s="152" t="s">
+      <c r="B40" s="168"/>
+      <c r="C40" s="166" t="s">
+        <v>152</v>
+      </c>
+      <c r="D40" s="166" t="s">
         <v>13</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G40" s="18">
         <f t="shared" si="2"/>
@@ -5045,9 +5105,9 @@
       </c>
       <c r="H40" s="7"/>
       <c r="I40" s="7"/>
-      <c r="J40" s="7"/>
-      <c r="K40" s="7"/>
-      <c r="L40" s="7"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="119"/>
+      <c r="L40" s="119"/>
       <c r="M40" s="7"/>
       <c r="N40" s="7"/>
       <c r="O40" s="19"/>
@@ -5057,15 +5117,15 @@
       <c r="S40" s="7"/>
     </row>
     <row r="41" spans="1:19" ht="20" customHeight="1">
-      <c r="A41" s="154"/>
-      <c r="B41" s="154"/>
-      <c r="C41" s="154"/>
-      <c r="D41" s="154"/>
+      <c r="A41" s="168"/>
+      <c r="B41" s="168"/>
+      <c r="C41" s="168"/>
+      <c r="D41" s="168"/>
       <c r="E41" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G41" s="18">
         <f t="shared" si="2"/>
@@ -5073,9 +5133,9 @@
       </c>
       <c r="H41" s="7"/>
       <c r="I41" s="7"/>
-      <c r="J41" s="7"/>
-      <c r="K41" s="7"/>
-      <c r="L41" s="7"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="119"/>
       <c r="M41" s="7"/>
       <c r="N41" s="7"/>
       <c r="O41" s="19"/>
@@ -5085,15 +5145,15 @@
       <c r="S41" s="7"/>
     </row>
     <row r="42" spans="1:19" ht="20" customHeight="1">
-      <c r="A42" s="154"/>
-      <c r="B42" s="154"/>
-      <c r="C42" s="154"/>
-      <c r="D42" s="154"/>
+      <c r="A42" s="168"/>
+      <c r="B42" s="168"/>
+      <c r="C42" s="168"/>
+      <c r="D42" s="168"/>
       <c r="E42" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G42" s="18">
         <f t="shared" si="2"/>
@@ -5101,9 +5161,9 @@
       </c>
       <c r="H42" s="7"/>
       <c r="I42" s="7"/>
-      <c r="J42" s="7"/>
-      <c r="K42" s="7"/>
-      <c r="L42" s="7"/>
+      <c r="J42" s="119"/>
+      <c r="K42" s="19"/>
+      <c r="L42" s="19"/>
       <c r="M42" s="7"/>
       <c r="N42" s="7"/>
       <c r="O42" s="7"/>
@@ -5113,15 +5173,15 @@
       <c r="S42" s="7"/>
     </row>
     <row r="43" spans="1:19" ht="20" customHeight="1">
-      <c r="A43" s="154"/>
-      <c r="B43" s="154"/>
-      <c r="C43" s="154"/>
-      <c r="D43" s="154"/>
+      <c r="A43" s="168"/>
+      <c r="B43" s="168"/>
+      <c r="C43" s="168"/>
+      <c r="D43" s="168"/>
       <c r="E43" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G43" s="18">
         <f t="shared" si="2"/>
@@ -5129,9 +5189,9 @@
       </c>
       <c r="H43" s="7"/>
       <c r="I43" s="7"/>
-      <c r="J43" s="7"/>
-      <c r="K43" s="7"/>
-      <c r="L43" s="7"/>
+      <c r="J43" s="119"/>
+      <c r="K43" s="19"/>
+      <c r="L43" s="19"/>
       <c r="M43" s="7"/>
       <c r="N43" s="7"/>
       <c r="O43" s="7"/>
@@ -5141,15 +5201,15 @@
       <c r="S43" s="7"/>
     </row>
     <row r="44" spans="1:19" ht="20" customHeight="1">
-      <c r="A44" s="153"/>
-      <c r="B44" s="153"/>
-      <c r="C44" s="153"/>
-      <c r="D44" s="153"/>
+      <c r="A44" s="167"/>
+      <c r="B44" s="167"/>
+      <c r="C44" s="167"/>
+      <c r="D44" s="167"/>
       <c r="E44" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G44" s="18">
         <f>COUNTIF(H44:S44,$T$2)/12</f>
@@ -5157,9 +5217,9 @@
       </c>
       <c r="H44" s="7"/>
       <c r="I44" s="7"/>
-      <c r="J44" s="7"/>
-      <c r="K44" s="7"/>
-      <c r="L44" s="7"/>
+      <c r="J44" s="119"/>
+      <c r="K44" s="119"/>
+      <c r="L44" s="19"/>
       <c r="M44" s="7"/>
       <c r="N44" s="7"/>
       <c r="O44" s="7"/>
@@ -5169,30 +5229,30 @@
       <c r="S44" s="7"/>
     </row>
     <row r="45" spans="1:19" ht="20" customHeight="1">
-      <c r="A45" s="152">
+      <c r="A45" s="166">
         <v>1</v>
       </c>
-      <c r="B45" s="152" t="s">
-        <v>161</v>
-      </c>
-      <c r="C45" s="152" t="s">
-        <v>162</v>
-      </c>
-      <c r="D45" s="152" t="s">
+      <c r="B45" s="166" t="s">
+        <v>158</v>
+      </c>
+      <c r="C45" s="166" t="s">
+        <v>159</v>
+      </c>
+      <c r="D45" s="166" t="s">
         <v>13</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G45" s="18">
         <f>COUNTIF(H45:S45,$T$2)/12</f>
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="H45" s="22" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I45" s="7"/>
       <c r="J45" s="7"/>
@@ -5207,25 +5267,27 @@
       <c r="S45" s="7"/>
     </row>
     <row r="46" spans="1:19" ht="20" customHeight="1">
-      <c r="A46" s="154"/>
-      <c r="B46" s="154"/>
-      <c r="C46" s="154"/>
-      <c r="D46" s="154"/>
+      <c r="A46" s="168"/>
+      <c r="B46" s="168"/>
+      <c r="C46" s="168"/>
+      <c r="D46" s="168"/>
       <c r="E46" s="8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G46" s="18">
         <f>COUNTIF(H46:S46,$T$2)/12</f>
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="H46" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="I46" s="22"/>
-      <c r="J46" s="13"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="H46" s="120" t="s">
+        <v>251</v>
+      </c>
+      <c r="I46" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="J46" s="174"/>
       <c r="K46" s="13"/>
       <c r="L46" s="13"/>
       <c r="M46" s="13"/>
@@ -5237,22 +5299,24 @@
       <c r="S46" s="13"/>
     </row>
     <row r="47" spans="1:19" ht="20" customHeight="1">
-      <c r="A47" s="153"/>
-      <c r="B47" s="154"/>
-      <c r="C47" s="153"/>
-      <c r="D47" s="153"/>
+      <c r="A47" s="167"/>
+      <c r="B47" s="168"/>
+      <c r="C47" s="167"/>
+      <c r="D47" s="167"/>
       <c r="E47" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F47" s="7" t="s">
         <v>91</v>
       </c>
       <c r="G47" s="18">
         <f t="shared" ref="G47:G57" si="3">COUNTIF(H47:S47,$T$2)/12</f>
-        <v>0</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="H47" s="7"/>
-      <c r="I47" s="22"/>
+      <c r="I47" s="22" t="s">
+        <v>251</v>
+      </c>
       <c r="J47" s="22"/>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
@@ -5265,21 +5329,21 @@
       <c r="S47" s="7"/>
     </row>
     <row r="48" spans="1:19" ht="20" customHeight="1">
-      <c r="A48" s="152">
+      <c r="A48" s="166">
         <v>2</v>
       </c>
-      <c r="B48" s="154"/>
-      <c r="C48" s="152" t="s">
-        <v>167</v>
-      </c>
-      <c r="D48" s="152" t="s">
+      <c r="B48" s="168"/>
+      <c r="C48" s="166" t="s">
+        <v>164</v>
+      </c>
+      <c r="D48" s="166" t="s">
         <v>8</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G48" s="18">
         <f t="shared" si="3"/>
@@ -5299,15 +5363,15 @@
       <c r="S48" s="7"/>
     </row>
     <row r="49" spans="1:19" ht="20" customHeight="1">
-      <c r="A49" s="154"/>
-      <c r="B49" s="154"/>
-      <c r="C49" s="154"/>
-      <c r="D49" s="154"/>
+      <c r="A49" s="168"/>
+      <c r="B49" s="168"/>
+      <c r="C49" s="168"/>
+      <c r="D49" s="168"/>
       <c r="E49" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G49" s="18">
         <f t="shared" si="3"/>
@@ -5327,15 +5391,15 @@
       <c r="S49" s="7"/>
     </row>
     <row r="50" spans="1:19" ht="20" customHeight="1">
-      <c r="A50" s="153"/>
-      <c r="B50" s="154"/>
-      <c r="C50" s="153"/>
-      <c r="D50" s="153"/>
+      <c r="A50" s="167"/>
+      <c r="B50" s="168"/>
+      <c r="C50" s="167"/>
+      <c r="D50" s="167"/>
       <c r="E50" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G50" s="18">
         <f t="shared" si="3"/>
@@ -5355,28 +5419,30 @@
       <c r="S50" s="7"/>
     </row>
     <row r="51" spans="1:19" ht="20" customHeight="1">
-      <c r="A51" s="152">
+      <c r="A51" s="166">
         <v>3</v>
       </c>
-      <c r="B51" s="154"/>
-      <c r="C51" s="152" t="s">
-        <v>171</v>
-      </c>
-      <c r="D51" s="152" t="s">
+      <c r="B51" s="168"/>
+      <c r="C51" s="166" t="s">
+        <v>168</v>
+      </c>
+      <c r="D51" s="166" t="s">
         <v>29</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G51" s="18">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="H51" s="24"/>
-      <c r="I51" s="24"/>
+      <c r="I51" s="24" t="s">
+        <v>251</v>
+      </c>
       <c r="J51" s="24"/>
       <c r="K51" s="24"/>
       <c r="L51" s="24"/>
@@ -5389,15 +5455,15 @@
       <c r="S51" s="24"/>
     </row>
     <row r="52" spans="1:19" ht="20" customHeight="1">
-      <c r="A52" s="154"/>
-      <c r="B52" s="154"/>
-      <c r="C52" s="154"/>
-      <c r="D52" s="154"/>
+      <c r="A52" s="168"/>
+      <c r="B52" s="168"/>
+      <c r="C52" s="168"/>
+      <c r="D52" s="168"/>
       <c r="E52" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G52" s="18">
         <f t="shared" si="3"/>
@@ -5417,15 +5483,15 @@
       <c r="S52" s="7"/>
     </row>
     <row r="53" spans="1:19" ht="20" customHeight="1">
-      <c r="A53" s="153"/>
-      <c r="B53" s="154"/>
-      <c r="C53" s="153"/>
-      <c r="D53" s="153"/>
+      <c r="A53" s="167"/>
+      <c r="B53" s="168"/>
+      <c r="C53" s="167"/>
+      <c r="D53" s="167"/>
       <c r="E53" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G53" s="18">
         <f t="shared" si="3"/>
@@ -5445,21 +5511,21 @@
       <c r="S53" s="7"/>
     </row>
     <row r="54" spans="1:19" ht="20" customHeight="1">
-      <c r="A54" s="152">
+      <c r="A54" s="166">
         <v>4</v>
       </c>
-      <c r="B54" s="154"/>
-      <c r="C54" s="152" t="s">
-        <v>175</v>
-      </c>
-      <c r="D54" s="152" t="s">
+      <c r="B54" s="168"/>
+      <c r="C54" s="166" t="s">
+        <v>172</v>
+      </c>
+      <c r="D54" s="166" t="s">
         <v>8</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G54" s="18">
         <f t="shared" si="3"/>
@@ -5479,15 +5545,15 @@
       <c r="S54" s="7"/>
     </row>
     <row r="55" spans="1:19" ht="20" customHeight="1">
-      <c r="A55" s="153"/>
-      <c r="B55" s="153"/>
-      <c r="C55" s="153"/>
-      <c r="D55" s="153"/>
+      <c r="A55" s="167"/>
+      <c r="B55" s="167"/>
+      <c r="C55" s="167"/>
+      <c r="D55" s="167"/>
       <c r="E55" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G55" s="18">
         <f t="shared" si="3"/>
@@ -5507,32 +5573,34 @@
       <c r="S55" s="19"/>
     </row>
     <row r="56" spans="1:19" ht="20" customHeight="1">
-      <c r="A56" s="152">
+      <c r="A56" s="166">
         <v>1</v>
       </c>
-      <c r="B56" s="152" t="s">
-        <v>179</v>
-      </c>
-      <c r="C56" s="152" t="s">
-        <v>180</v>
-      </c>
-      <c r="D56" s="151" t="s">
+      <c r="B56" s="166" t="s">
+        <v>176</v>
+      </c>
+      <c r="C56" s="166" t="s">
+        <v>177</v>
+      </c>
+      <c r="D56" s="165" t="s">
         <v>29</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G56" s="18">
         <f t="shared" si="3"/>
-        <v>8.3333333333333329E-2</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="H56" s="23" t="s">
-        <v>93</v>
-      </c>
-      <c r="I56" s="23"/>
+        <v>92</v>
+      </c>
+      <c r="I56" s="23" t="s">
+        <v>251</v>
+      </c>
       <c r="J56" s="23"/>
       <c r="K56" s="23"/>
       <c r="L56" s="23"/>
@@ -5545,15 +5613,15 @@
       <c r="S56" s="23"/>
     </row>
     <row r="57" spans="1:19" ht="20" customHeight="1">
-      <c r="A57" s="153"/>
-      <c r="B57" s="153"/>
-      <c r="C57" s="153"/>
-      <c r="D57" s="151"/>
+      <c r="A57" s="167"/>
+      <c r="B57" s="167"/>
+      <c r="C57" s="167"/>
+      <c r="D57" s="165"/>
       <c r="E57" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G57" s="18">
         <f t="shared" si="3"/>
@@ -5682,45 +5750,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="48" customHeight="1">
-      <c r="A1" s="155" t="s">
-        <v>183</v>
-      </c>
-      <c r="B1" s="155"/>
-      <c r="C1" s="155"/>
-      <c r="D1" s="155"/>
-      <c r="E1" s="155"/>
-      <c r="F1" s="155"/>
-      <c r="G1" s="155"/>
-      <c r="H1" s="155"/>
-      <c r="I1" s="155"/>
-      <c r="J1" s="155"/>
-      <c r="K1" s="155"/>
-      <c r="L1" s="155"/>
-      <c r="M1" s="155"/>
-      <c r="N1" s="155"/>
-      <c r="O1" s="155"/>
-      <c r="P1" s="155"/>
-      <c r="Q1" s="155"/>
-      <c r="R1" s="155"/>
-      <c r="S1" s="155"/>
-      <c r="T1" s="155"/>
-      <c r="U1" s="155"/>
-      <c r="V1" s="155"/>
-      <c r="W1" s="155"/>
-      <c r="X1" s="155"/>
-      <c r="Y1" s="155"/>
-      <c r="Z1" s="155"/>
-      <c r="AA1" s="155"/>
-      <c r="AB1" s="155"/>
-      <c r="AC1" s="155"/>
-      <c r="AD1" s="155"/>
-      <c r="AE1" s="155"/>
-      <c r="AF1" s="155"/>
-      <c r="AG1" s="155"/>
-      <c r="AH1" s="155"/>
-      <c r="AI1" s="155"/>
-      <c r="AJ1" s="155"/>
-      <c r="AK1" s="155"/>
+      <c r="A1" s="169" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1" s="169"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="169"/>
+      <c r="H1" s="169"/>
+      <c r="I1" s="169"/>
+      <c r="J1" s="169"/>
+      <c r="K1" s="169"/>
+      <c r="L1" s="169"/>
+      <c r="M1" s="169"/>
+      <c r="N1" s="169"/>
+      <c r="O1" s="169"/>
+      <c r="P1" s="169"/>
+      <c r="Q1" s="169"/>
+      <c r="R1" s="169"/>
+      <c r="S1" s="169"/>
+      <c r="T1" s="169"/>
+      <c r="U1" s="169"/>
+      <c r="V1" s="169"/>
+      <c r="W1" s="169"/>
+      <c r="X1" s="169"/>
+      <c r="Y1" s="169"/>
+      <c r="Z1" s="169"/>
+      <c r="AA1" s="169"/>
+      <c r="AB1" s="169"/>
+      <c r="AC1" s="169"/>
+      <c r="AD1" s="169"/>
+      <c r="AE1" s="169"/>
+      <c r="AF1" s="169"/>
+      <c r="AG1" s="169"/>
+      <c r="AH1" s="169"/>
+      <c r="AI1" s="169"/>
+      <c r="AJ1" s="169"/>
+      <c r="AK1" s="169"/>
     </row>
     <row r="2" spans="1:37" ht="18">
       <c r="A2" s="5" t="s">
@@ -5742,111 +5810,111 @@
         <v>74</v>
       </c>
       <c r="G2" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="J2" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="P2" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="Q2" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="R2" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="S2" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="T2" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="U2" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="V2" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="T2" s="5" t="s">
+      <c r="W2" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="U2" s="5" t="s">
+      <c r="X2" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="V2" s="5" t="s">
+      <c r="Y2" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="W2" s="5" t="s">
+      <c r="Z2" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="X2" s="5" t="s">
+      <c r="AA2" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="Y2" s="5" t="s">
+      <c r="AB2" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="Z2" s="5" t="s">
+      <c r="AC2" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="AA2" s="5" t="s">
+      <c r="AD2" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="AB2" s="5" t="s">
+      <c r="AE2" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="AC2" s="5" t="s">
+      <c r="AF2" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="AD2" s="5" t="s">
+      <c r="AG2" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="AE2" s="5" t="s">
+      <c r="AH2" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="AF2" s="5" t="s">
+      <c r="AI2" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="AG2" s="5" t="s">
+      <c r="AJ2" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="AH2" s="5" t="s">
+      <c r="AK2" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="AI2" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ2" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="AK2" s="5" t="s">
-        <v>214</v>
-      </c>
     </row>
     <row r="3" spans="1:37" ht="18">
-      <c r="A3" s="152">
+      <c r="A3" s="166">
         <v>1</v>
       </c>
-      <c r="B3" s="151" t="s">
+      <c r="B3" s="165" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3" s="165" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="C3" s="151" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>102</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>91</v>
@@ -5856,215 +5924,215 @@
         <v>0.12903225806451613</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="L3" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N3" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O3" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P3" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q3" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R3" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S3" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T3" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U3" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V3" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W3" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X3" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y3" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Z3" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AA3" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB3" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AC3" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AD3" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AE3" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AF3" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG3" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AH3" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AI3" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AJ3" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AK3" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:37" ht="18">
-      <c r="A4" s="153"/>
-      <c r="B4" s="151"/>
-      <c r="C4" s="151"/>
+      <c r="A4" s="167"/>
+      <c r="B4" s="165"/>
+      <c r="C4" s="165"/>
       <c r="D4" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>103</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>104</v>
       </c>
       <c r="F4" s="11">
         <f t="shared" ref="F4:F18" si="0">COUNTIF(G4:AJ4,$I$3)/31</f>
         <v>0</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Z4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AA4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AC4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AD4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AE4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AF4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AH4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AI4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AJ4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AK4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:37" ht="30">
-      <c r="A5" s="152">
+      <c r="A5" s="166">
         <v>2</v>
       </c>
-      <c r="B5" s="151"/>
-      <c r="C5" s="151"/>
+      <c r="B5" s="165"/>
+      <c r="C5" s="165"/>
       <c r="D5" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>91</v>
@@ -6074,565 +6142,565 @@
         <v>3.2258064516129031E-2</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O5" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="P5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Z5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AA5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AC5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AD5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AE5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AF5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AH5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AI5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AJ5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AK5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:37" ht="18">
-      <c r="A6" s="153"/>
-      <c r="B6" s="151" t="s">
+      <c r="A6" s="167"/>
+      <c r="B6" s="165" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="165" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>123</v>
-      </c>
-      <c r="C6" s="151" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>125</v>
       </c>
       <c r="F6" s="11">
         <f>COUNTIF(G6:AJ6,$I$3)/3</f>
         <v>1</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M6" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N6" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O6" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P6" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q6" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R6" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S6" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T6" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U6" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V6" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W6" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="X6" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Y6" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="Z6" s="156"/>
-      <c r="AA6" s="157"/>
-      <c r="AB6" s="157"/>
-      <c r="AC6" s="157"/>
-      <c r="AD6" s="157"/>
-      <c r="AE6" s="157"/>
-      <c r="AF6" s="157"/>
-      <c r="AG6" s="157"/>
-      <c r="AH6" s="157"/>
-      <c r="AI6" s="157"/>
-      <c r="AJ6" s="157"/>
-      <c r="AK6" s="158"/>
+        <v>213</v>
+      </c>
+      <c r="Z6" s="170"/>
+      <c r="AA6" s="171"/>
+      <c r="AB6" s="171"/>
+      <c r="AC6" s="171"/>
+      <c r="AD6" s="171"/>
+      <c r="AE6" s="171"/>
+      <c r="AF6" s="171"/>
+      <c r="AG6" s="171"/>
+      <c r="AH6" s="171"/>
+      <c r="AI6" s="171"/>
+      <c r="AJ6" s="171"/>
+      <c r="AK6" s="172"/>
     </row>
     <row r="7" spans="1:37" ht="18">
       <c r="A7" s="7">
         <v>3</v>
       </c>
-      <c r="B7" s="151"/>
-      <c r="C7" s="151"/>
+      <c r="B7" s="165"/>
+      <c r="C7" s="165"/>
       <c r="D7" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F7" s="11">
         <f>COUNTIF(G7:AJ7,$I$3)/4</f>
         <v>1</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M7" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O7" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="P7" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q7" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R7" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S7" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T7" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U7" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V7" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W7" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="X7" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Y7" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="Z7" s="156"/>
-      <c r="AA7" s="157"/>
-      <c r="AB7" s="157"/>
-      <c r="AC7" s="157"/>
-      <c r="AD7" s="157"/>
-      <c r="AE7" s="157"/>
-      <c r="AF7" s="157"/>
-      <c r="AG7" s="157"/>
-      <c r="AH7" s="157"/>
-      <c r="AI7" s="157"/>
-      <c r="AJ7" s="157"/>
-      <c r="AK7" s="158"/>
+        <v>213</v>
+      </c>
+      <c r="Z7" s="170"/>
+      <c r="AA7" s="171"/>
+      <c r="AB7" s="171"/>
+      <c r="AC7" s="171"/>
+      <c r="AD7" s="171"/>
+      <c r="AE7" s="171"/>
+      <c r="AF7" s="171"/>
+      <c r="AG7" s="171"/>
+      <c r="AH7" s="171"/>
+      <c r="AI7" s="171"/>
+      <c r="AJ7" s="171"/>
+      <c r="AK7" s="172"/>
     </row>
     <row r="8" spans="1:37" ht="22">
       <c r="A8" s="7">
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F8" s="11">
         <f>COUNTIF(G8:AJ8,$I$3)/4</f>
         <v>0.75</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L8" s="103" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="M8" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N8" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="O8" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="P8" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q8" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R8" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S8" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T8" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U8" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="V8" s="156"/>
-      <c r="W8" s="157"/>
-      <c r="X8" s="157"/>
-      <c r="Y8" s="157"/>
-      <c r="Z8" s="157"/>
-      <c r="AA8" s="157"/>
-      <c r="AB8" s="157"/>
-      <c r="AC8" s="157"/>
-      <c r="AD8" s="157"/>
-      <c r="AE8" s="157"/>
-      <c r="AF8" s="157"/>
-      <c r="AG8" s="157"/>
-      <c r="AH8" s="157"/>
-      <c r="AI8" s="157"/>
-      <c r="AJ8" s="157"/>
-      <c r="AK8" s="158"/>
+        <v>213</v>
+      </c>
+      <c r="V8" s="170"/>
+      <c r="W8" s="171"/>
+      <c r="X8" s="171"/>
+      <c r="Y8" s="171"/>
+      <c r="Z8" s="171"/>
+      <c r="AA8" s="171"/>
+      <c r="AB8" s="171"/>
+      <c r="AC8" s="171"/>
+      <c r="AD8" s="171"/>
+      <c r="AE8" s="171"/>
+      <c r="AF8" s="171"/>
+      <c r="AG8" s="171"/>
+      <c r="AH8" s="171"/>
+      <c r="AI8" s="171"/>
+      <c r="AJ8" s="171"/>
+      <c r="AK8" s="172"/>
     </row>
     <row r="9" spans="1:37" ht="26" customHeight="1">
       <c r="A9" s="7">
         <v>5</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F9" s="11">
         <f>COUNTIF(G9:AJ9,$I$3)/2</f>
         <v>1</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L9" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M9" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N9" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O9" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P9" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q9" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R9" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S9" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T9" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="U9" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V9" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W9" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X9" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y9" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="Z9" s="156"/>
-      <c r="AA9" s="157"/>
-      <c r="AB9" s="157"/>
-      <c r="AC9" s="157"/>
-      <c r="AD9" s="157"/>
-      <c r="AE9" s="157"/>
-      <c r="AF9" s="157"/>
-      <c r="AG9" s="157"/>
-      <c r="AH9" s="157"/>
-      <c r="AI9" s="157"/>
-      <c r="AJ9" s="157"/>
-      <c r="AK9" s="158"/>
+        <v>213</v>
+      </c>
+      <c r="Z9" s="170"/>
+      <c r="AA9" s="171"/>
+      <c r="AB9" s="171"/>
+      <c r="AC9" s="171"/>
+      <c r="AD9" s="171"/>
+      <c r="AE9" s="171"/>
+      <c r="AF9" s="171"/>
+      <c r="AG9" s="171"/>
+      <c r="AH9" s="171"/>
+      <c r="AI9" s="171"/>
+      <c r="AJ9" s="171"/>
+      <c r="AK9" s="172"/>
     </row>
     <row r="10" spans="1:37" ht="21" customHeight="1">
-      <c r="A10" s="154">
+      <c r="A10" s="168">
         <v>6</v>
       </c>
-      <c r="B10" s="152" t="s">
-        <v>142</v>
+      <c r="B10" s="166" t="s">
+        <v>139</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F10" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Z10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AA10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AC10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AD10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AE10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AF10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AH10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AI10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AJ10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AK10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:37" ht="23" customHeight="1">
-      <c r="A11" s="153"/>
-      <c r="B11" s="153"/>
+      <c r="A11" s="167"/>
+      <c r="B11" s="167"/>
       <c r="C11" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>91</v>
@@ -6642,765 +6710,765 @@
         <v>0.12903225806451613</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M11" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N11" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="O11" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="P11" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Q11" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R11" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S11" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T11" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U11" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V11" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W11" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X11" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y11" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Z11" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AA11" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB11" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AC11" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AD11" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AE11" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AF11" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG11" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AH11" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AI11" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AJ11" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AK11" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12" spans="1:37" ht="18">
       <c r="A12" s="7">
         <v>7</v>
       </c>
-      <c r="B12" s="152" t="s">
-        <v>146</v>
-      </c>
-      <c r="C12" s="151" t="s">
+      <c r="B12" s="166" t="s">
+        <v>143</v>
+      </c>
+      <c r="C12" s="165" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F12" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Z12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AA12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AC12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AD12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AE12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AF12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AH12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AI12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AJ12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AK12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13" spans="1:37" ht="18">
       <c r="A13" s="7">
         <v>8</v>
       </c>
-      <c r="B13" s="154"/>
-      <c r="C13" s="151"/>
+      <c r="B13" s="168"/>
+      <c r="C13" s="165"/>
       <c r="D13" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F13" s="11">
         <f t="shared" si="0"/>
         <v>9.6774193548387094E-2</v>
       </c>
       <c r="G13" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="M13" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="N13" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="O13" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="P13" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q13" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="R13" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="S13" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="T13" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="U13" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="V13" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="W13" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="X13" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="Y13" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="Z13" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="AA13" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="AB13" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="AC13" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="AD13" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="AE13" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="AF13" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="AG13" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="AH13" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="AI13" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ13" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="AK13" s="12" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37" ht="18">
+      <c r="A14" s="166">
+        <v>9</v>
+      </c>
+      <c r="B14" s="166" t="s">
+        <v>159</v>
+      </c>
+      <c r="C14" s="166" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="H13" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="K13" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="L13" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="M13" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="N13" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="O13" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="P13" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q13" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="R13" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="S13" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="T13" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="U13" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="V13" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="W13" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="X13" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="Y13" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z13" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="AA13" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB13" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC13" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="AD13" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="AE13" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="AF13" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="AG13" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="AH13" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="AI13" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="AJ13" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="AK13" s="12" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="14" spans="1:37" ht="18">
-      <c r="A14" s="152">
-        <v>9</v>
-      </c>
-      <c r="B14" s="152" t="s">
-        <v>162</v>
-      </c>
-      <c r="C14" s="152" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>218</v>
-      </c>
       <c r="E14" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F14" s="11">
         <f t="shared" si="0"/>
         <v>0.19354838709677419</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L14" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M14" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N14" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O14" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P14" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q14" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R14" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S14" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T14" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="U14" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="V14" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="W14" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="X14" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="Y14" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="Z14" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="AA14" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="AB14" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="AC14" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="AD14" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="AE14" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="AF14" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="AG14" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="AH14" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="AI14" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ14" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="AK14" s="12" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37" ht="18">
+      <c r="A15" s="167"/>
+      <c r="B15" s="168"/>
+      <c r="C15" s="168"/>
+      <c r="D15" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="U14" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="V14" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="W14" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="X14" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y14" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z14" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="AA14" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB14" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC14" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="AD14" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="AE14" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="AF14" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="AG14" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="AH14" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="AI14" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="AJ14" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="AK14" s="12" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="15" spans="1:37" ht="18">
-      <c r="A15" s="153"/>
-      <c r="B15" s="154"/>
-      <c r="C15" s="154"/>
-      <c r="D15" s="8" t="s">
-        <v>219</v>
-      </c>
       <c r="E15" s="13" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F15" s="11">
         <f t="shared" si="0"/>
         <v>0.19354838709677419</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M15" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N15" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O15" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P15" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q15" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R15" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S15" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="T15" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="U15" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V15" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="W15" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X15" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Y15" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Z15" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AA15" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB15" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AC15" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AD15" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AE15" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AF15" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG15" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AH15" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AI15" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AJ15" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AK15" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="1:37" ht="18">
-      <c r="A16" s="151">
+      <c r="A16" s="165">
         <v>10</v>
       </c>
-      <c r="B16" s="151" t="s">
-        <v>171</v>
-      </c>
-      <c r="C16" s="152" t="s">
+      <c r="B16" s="165" t="s">
+        <v>168</v>
+      </c>
+      <c r="C16" s="166" t="s">
         <v>29</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F16" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Z16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AA16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AC16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AD16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AE16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AF16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AH16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AI16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AJ16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AK16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17" spans="1:37" ht="18">
-      <c r="A17" s="151"/>
-      <c r="B17" s="151"/>
-      <c r="C17" s="154"/>
+      <c r="A17" s="165"/>
+      <c r="B17" s="165"/>
+      <c r="C17" s="168"/>
       <c r="D17" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F17" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Z17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AA17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AC17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AD17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AE17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AF17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AH17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AI17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AJ17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AK17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18" spans="1:37" ht="18">
@@ -7408,113 +7476,113 @@
         <v>11</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F18" s="11">
         <f t="shared" si="0"/>
         <v>0.12903225806451613</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M18" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N18" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O18" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P18" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q18" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R18" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S18" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T18" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U18" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="V18" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="W18" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="X18" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y18" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Z18" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AA18" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB18" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AC18" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AD18" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AE18" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AF18" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG18" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AH18" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AI18" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AJ18" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AK18" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -7595,14 +7663,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="48" customHeight="1">
-      <c r="A1" s="155" t="s">
-        <v>183</v>
-      </c>
-      <c r="B1" s="155"/>
-      <c r="C1" s="155"/>
-      <c r="D1" s="155"/>
-      <c r="E1" s="155"/>
-      <c r="F1" s="155"/>
+      <c r="A1" s="169" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1" s="169"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
@@ -7652,105 +7720,105 @@
         <v>74</v>
       </c>
       <c r="G2" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="J2" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="P2" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="Q2" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="R2" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="S2" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="T2" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="U2" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="V2" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="T2" s="5" t="s">
+      <c r="W2" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="U2" s="5" t="s">
+      <c r="X2" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="V2" s="5" t="s">
+      <c r="Y2" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="W2" s="5" t="s">
+      <c r="Z2" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="X2" s="5" t="s">
+      <c r="AA2" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="Y2" s="5" t="s">
+      <c r="AB2" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="Z2" s="5" t="s">
+      <c r="AC2" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="AA2" s="5" t="s">
+      <c r="AD2" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="AB2" s="5" t="s">
+      <c r="AE2" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="AC2" s="5" t="s">
+      <c r="AF2" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="AD2" s="5" t="s">
+      <c r="AG2" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="AE2" s="5" t="s">
+      <c r="AH2" s="5" t="s">
         <v>208</v>
-      </c>
-      <c r="AF2" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="AG2" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="AH2" s="5" t="s">
-        <v>211</v>
       </c>
       <c r="AI2" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:35" ht="18">
-      <c r="A3" s="152">
+      <c r="A3" s="166">
         <v>1</v>
       </c>
-      <c r="B3" s="152" t="s">
-        <v>221</v>
-      </c>
-      <c r="C3" s="152" t="s">
+      <c r="B3" s="166" t="s">
+        <v>218</v>
+      </c>
+      <c r="C3" s="166" t="s">
         <v>29</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="11">
@@ -7758,97 +7826,97 @@
         <v>0.17857142857142858</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I3" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J3" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K3" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L3" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M3" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N3" s="89" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="O3" s="89" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="P3" s="89" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Q3" s="89" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="R3" s="89" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S3" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T3" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U3" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V3" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W3" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X3" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y3" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Z3" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AA3" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB3" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AC3" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AD3" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AE3" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AF3" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG3" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AH3" s="15"/>
       <c r="AI3" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" spans="1:35" ht="18">
-      <c r="A4" s="153"/>
-      <c r="B4" s="153"/>
-      <c r="C4" s="153"/>
+      <c r="A4" s="167"/>
+      <c r="B4" s="167"/>
+      <c r="C4" s="167"/>
       <c r="D4" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="11">
@@ -7856,100 +7924,100 @@
         <v>0.17857142857142858</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I4" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J4" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K4" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L4" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M4" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N4" s="89" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="O4" s="89" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="P4" s="89" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Q4" s="89" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="R4" s="89" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S4" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T4" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U4" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V4" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W4" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X4" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y4" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Z4" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AA4" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB4" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AC4" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AD4" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AE4" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AF4" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG4" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AH4" s="15"/>
     </row>
     <row r="5" spans="1:35" ht="21" customHeight="1">
-      <c r="A5" s="154">
+      <c r="A5" s="168">
         <v>2</v>
       </c>
-      <c r="B5" s="152" t="s">
-        <v>222</v>
+      <c r="B5" s="166" t="s">
+        <v>219</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="11">
@@ -7957,96 +8025,96 @@
         <v>0</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I5" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J5" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K5" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L5" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M5" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N5" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O5" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P5" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q5" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R5" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S5" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T5" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U5" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V5" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W5" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X5" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y5" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Z5" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AA5" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB5" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AC5" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AD5" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AE5" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AF5" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG5" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AH5" s="15"/>
     </row>
     <row r="6" spans="1:35" ht="23" customHeight="1">
-      <c r="A6" s="153"/>
-      <c r="B6" s="153"/>
+      <c r="A6" s="167"/>
+      <c r="B6" s="167"/>
       <c r="C6" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="11">
@@ -8054,100 +8122,100 @@
         <v>0</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I6" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J6" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K6" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L6" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M6" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N6" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O6" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P6" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q6" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R6" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S6" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T6" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U6" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V6" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W6" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X6" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y6" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Z6" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AA6" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB6" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AC6" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AD6" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AE6" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AF6" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG6" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AH6" s="15"/>
     </row>
     <row r="7" spans="1:35" ht="18">
-      <c r="A7" s="152">
+      <c r="A7" s="166">
         <v>3</v>
       </c>
-      <c r="B7" s="152" t="s">
-        <v>146</v>
-      </c>
-      <c r="C7" s="152" t="s">
+      <c r="B7" s="166" t="s">
+        <v>143</v>
+      </c>
+      <c r="C7" s="166" t="s">
         <v>29</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="11">
@@ -8155,94 +8223,94 @@
         <v>0</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I7" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J7" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K7" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L7" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M7" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N7" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O7" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P7" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q7" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R7" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S7" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T7" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U7" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V7" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W7" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X7" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y7" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Z7" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AA7" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB7" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AC7" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AD7" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AE7" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AF7" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG7" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AH7" s="15"/>
     </row>
     <row r="8" spans="1:35" ht="18">
-      <c r="A8" s="153"/>
-      <c r="B8" s="154"/>
-      <c r="C8" s="153"/>
+      <c r="A8" s="167"/>
+      <c r="B8" s="168"/>
+      <c r="C8" s="167"/>
       <c r="D8" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="11">
@@ -8250,100 +8318,100 @@
         <v>0</v>
       </c>
       <c r="G8" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="I8" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="J8" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="K8" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="L8" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="M8" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="N8" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="O8" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="P8" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q8" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="R8" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="S8" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="T8" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="U8" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="V8" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="W8" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="X8" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="Y8" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="Z8" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="AA8" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="AB8" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="AC8" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="AD8" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="AE8" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="AF8" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="AG8" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="AH8" s="15"/>
+    </row>
+    <row r="9" spans="1:35" ht="18">
+      <c r="A9" s="166">
+        <v>4</v>
+      </c>
+      <c r="B9" s="166" t="s">
+        <v>159</v>
+      </c>
+      <c r="C9" s="166" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>215</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="I8" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="J8" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="K8" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="L8" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="M8" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="N8" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="O8" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="P8" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q8" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="R8" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="S8" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="T8" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="U8" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="V8" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="W8" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="X8" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="Y8" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z8" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="AA8" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB8" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC8" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="AD8" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="AE8" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="AF8" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="AG8" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="AH8" s="15"/>
-    </row>
-    <row r="9" spans="1:35" ht="18">
-      <c r="A9" s="152">
-        <v>4</v>
-      </c>
-      <c r="B9" s="152" t="s">
-        <v>162</v>
-      </c>
-      <c r="C9" s="152" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>218</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="11">
@@ -8351,94 +8419,94 @@
         <v>3.5714285714285712E-2</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I9" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J9" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K9" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L9" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M9" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N9" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O9" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P9" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q9" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R9" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S9" s="89" t="s">
+        <v>213</v>
+      </c>
+      <c r="T9" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="U9" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="V9" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="W9" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="X9" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="Y9" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="Z9" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="AA9" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="AB9" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="AC9" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="AD9" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="AE9" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="AF9" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="AG9" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="AH9" s="15"/>
+    </row>
+    <row r="10" spans="1:35" ht="18">
+      <c r="A10" s="168"/>
+      <c r="B10" s="168"/>
+      <c r="C10" s="168"/>
+      <c r="D10" s="8" t="s">
         <v>216</v>
-      </c>
-      <c r="T9" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="U9" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="V9" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="W9" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="X9" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="Y9" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z9" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="AA9" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB9" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC9" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="AD9" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="AE9" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="AF9" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="AG9" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="AH9" s="15"/>
-    </row>
-    <row r="10" spans="1:35" ht="18">
-      <c r="A10" s="154"/>
-      <c r="B10" s="154"/>
-      <c r="C10" s="154"/>
-      <c r="D10" s="8" t="s">
-        <v>219</v>
       </c>
       <c r="E10" s="13"/>
       <c r="F10" s="11">
@@ -8446,94 +8514,94 @@
         <v>0.21428571428571427</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I10" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J10" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K10" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L10" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M10" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N10" s="89" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="O10" s="89" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="P10" s="89" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Q10" s="89" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="R10" s="89" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S10" s="89" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="T10" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U10" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V10" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W10" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X10" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y10" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Z10" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AA10" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB10" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AC10" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AD10" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AE10" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AF10" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG10" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AH10" s="15"/>
     </row>
     <row r="11" spans="1:35" ht="18">
-      <c r="A11" s="153"/>
-      <c r="B11" s="154"/>
-      <c r="C11" s="154"/>
+      <c r="A11" s="167"/>
+      <c r="B11" s="168"/>
+      <c r="C11" s="168"/>
       <c r="D11" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E11" s="13"/>
       <c r="F11" s="11">
@@ -8541,100 +8609,100 @@
         <v>3.5714285714285712E-2</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I11" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J11" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K11" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L11" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M11" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N11" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O11" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P11" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q11" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R11" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S11" s="89" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="T11" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U11" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V11" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W11" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X11" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y11" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Z11" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AA11" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB11" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AC11" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AD11" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AE11" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AF11" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG11" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AH11" s="15"/>
     </row>
     <row r="12" spans="1:35" ht="18">
-      <c r="A12" s="152">
+      <c r="A12" s="166">
         <v>5</v>
       </c>
-      <c r="B12" s="152" t="s">
-        <v>171</v>
-      </c>
-      <c r="C12" s="152" t="s">
+      <c r="B12" s="166" t="s">
+        <v>168</v>
+      </c>
+      <c r="C12" s="166" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E12" s="7"/>
       <c r="F12" s="11">
@@ -8642,94 +8710,94 @@
         <v>0</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I12" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J12" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K12" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L12" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M12" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N12" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O12" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P12" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q12" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R12" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S12" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T12" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U12" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V12" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W12" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X12" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y12" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Z12" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AA12" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB12" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AC12" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AD12" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AE12" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AF12" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG12" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AH12" s="15"/>
     </row>
     <row r="13" spans="1:35" ht="18">
-      <c r="A13" s="153"/>
-      <c r="B13" s="153"/>
-      <c r="C13" s="154"/>
+      <c r="A13" s="167"/>
+      <c r="B13" s="167"/>
+      <c r="C13" s="168"/>
       <c r="D13" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E13" s="7"/>
       <c r="F13" s="11">
@@ -8737,85 +8805,85 @@
         <v>0</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I13" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J13" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K13" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L13" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M13" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N13" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O13" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P13" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q13" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R13" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S13" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T13" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U13" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V13" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W13" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X13" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y13" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Z13" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AA13" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB13" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AC13" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AD13" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AE13" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AF13" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG13" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AH13" s="15"/>
     </row>
@@ -8824,13 +8892,13 @@
         <v>6</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="11">
@@ -8838,97 +8906,97 @@
         <v>0</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I14" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J14" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K14" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L14" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M14" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N14" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O14" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P14" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q14" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R14" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S14" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T14" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U14" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V14" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W14" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X14" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y14" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Z14" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AA14" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB14" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AC14" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AD14" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AE14" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AF14" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG14" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AH14" s="15"/>
     </row>
     <row r="15" spans="1:35" ht="30">
-      <c r="A15" s="152">
+      <c r="A15" s="166">
         <v>7</v>
       </c>
-      <c r="B15" s="151" t="s">
+      <c r="B15" s="165" t="s">
         <v>89</v>
       </c>
-      <c r="C15" s="151" t="s">
-        <v>242</v>
+      <c r="C15" s="165" t="s">
+        <v>239</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>90</v>
@@ -8939,94 +9007,94 @@
         <v>0</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I15" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J15" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K15" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L15" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M15" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N15" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O15" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P15" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q15" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R15" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S15" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T15" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U15" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V15" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W15" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X15" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y15" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Z15" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AA15" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB15" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AC15" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AD15" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AE15" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AF15" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG15" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AH15" s="14"/>
     </row>
     <row r="16" spans="1:35" ht="18">
-      <c r="A16" s="154"/>
-      <c r="B16" s="151"/>
-      <c r="C16" s="151"/>
+      <c r="A16" s="168"/>
+      <c r="B16" s="165"/>
+      <c r="C16" s="165"/>
       <c r="D16" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="11">
@@ -9034,94 +9102,94 @@
         <v>0</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I16" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J16" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K16" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L16" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M16" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N16" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O16" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P16" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q16" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R16" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S16" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T16" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U16" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V16" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W16" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X16" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y16" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Z16" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AA16" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB16" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AC16" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AD16" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AE16" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AF16" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG16" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AH16" s="14"/>
     </row>
     <row r="17" spans="1:34" ht="18">
-      <c r="A17" s="154"/>
-      <c r="B17" s="151"/>
-      <c r="C17" s="151"/>
+      <c r="A17" s="168"/>
+      <c r="B17" s="165"/>
+      <c r="C17" s="165"/>
       <c r="D17" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E17" s="9"/>
       <c r="F17" s="11">
@@ -9129,94 +9197,94 @@
         <v>0</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I17" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J17" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K17" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L17" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M17" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N17" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O17" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P17" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q17" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R17" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S17" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T17" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U17" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V17" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W17" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X17" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y17" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Z17" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AA17" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB17" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AC17" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AD17" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AE17" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AF17" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG17" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AH17" s="14"/>
     </row>
     <row r="18" spans="1:34" ht="18">
-      <c r="A18" s="153"/>
-      <c r="B18" s="151"/>
-      <c r="C18" s="151"/>
+      <c r="A18" s="167"/>
+      <c r="B18" s="165"/>
+      <c r="C18" s="165"/>
       <c r="D18" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E18" s="9"/>
       <c r="F18" s="11">
@@ -9224,100 +9292,100 @@
         <v>0</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I18" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J18" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K18" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L18" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M18" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N18" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O18" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P18" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q18" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R18" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S18" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T18" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U18" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V18" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W18" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X18" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y18" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Z18" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AA18" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB18" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AC18" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AD18" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AE18" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AF18" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG18" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AH18" s="14"/>
     </row>
     <row r="19" spans="1:34" ht="18">
-      <c r="A19" s="152">
+      <c r="A19" s="166">
         <v>8</v>
       </c>
-      <c r="B19" s="151" t="s">
+      <c r="B19" s="165" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" s="165" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="C19" s="151" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="E19" s="9"/>
       <c r="F19" s="11">
@@ -9325,94 +9393,94 @@
         <v>0</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I19" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J19" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K19" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L19" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M19" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N19" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O19" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P19" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q19" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R19" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S19" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T19" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U19" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V19" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W19" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X19" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y19" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Z19" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AA19" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB19" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AC19" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AD19" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AE19" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AF19" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG19" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AH19" s="14"/>
     </row>
     <row r="20" spans="1:34" ht="18">
-      <c r="A20" s="154"/>
-      <c r="B20" s="151"/>
-      <c r="C20" s="151"/>
+      <c r="A20" s="168"/>
+      <c r="B20" s="165"/>
+      <c r="C20" s="165"/>
       <c r="D20" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E20" s="9"/>
       <c r="F20" s="11">
@@ -9420,94 +9488,94 @@
         <v>0</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I20" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J20" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K20" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L20" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M20" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N20" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O20" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P20" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q20" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R20" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S20" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T20" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U20" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V20" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W20" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X20" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y20" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Z20" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AA20" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB20" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AC20" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AD20" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AE20" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AF20" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG20" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AH20" s="14"/>
     </row>
     <row r="21" spans="1:34" ht="18">
-      <c r="A21" s="153"/>
-      <c r="B21" s="151"/>
-      <c r="C21" s="151"/>
+      <c r="A21" s="167"/>
+      <c r="B21" s="165"/>
+      <c r="C21" s="165"/>
       <c r="D21" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E21" s="9"/>
       <c r="F21" s="11">
@@ -9515,85 +9583,85 @@
         <v>0</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I21" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J21" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K21" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L21" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M21" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N21" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O21" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P21" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q21" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R21" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S21" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T21" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U21" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V21" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W21" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X21" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y21" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Z21" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AA21" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB21" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AC21" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AD21" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AE21" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AF21" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG21" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AH21" s="14"/>
     </row>
@@ -9602,13 +9670,13 @@
         <v>9</v>
       </c>
       <c r="B22" s="104" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C22" s="104" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E22" s="104"/>
       <c r="F22" s="11">
@@ -9629,46 +9697,46 @@
       <c r="R22" s="105"/>
       <c r="S22" s="105"/>
       <c r="T22" s="89" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="U22" s="89" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="V22" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W22" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X22" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y22" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Z22" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AA22" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB22" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AC22" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AD22" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AE22" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AF22" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG22" s="89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AH22" s="15"/>
     </row>
@@ -9732,4 +9800,14 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82E1CC3B-4C12-A842-9893-EC3E3A4F43FC}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData/>
+  <phoneticPr fontId="13" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>